--- a/00_GESTION_DE_PROJET/01_Cadrage/Matrice RACI.xlsx
+++ b/00_GESTION_DE_PROJET/01_Cadrage/Matrice RACI.xlsx
@@ -745,7 +745,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P102"/>
+  <dimension ref="A1:P123"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="10.86" customWidth="1" style="55" min="1" max="1"/>
@@ -1678,20 +1678,36 @@
       </c>
       <c r="B25" s="27" t="inlineStr">
         <is>
-          <t>IA de Lecture</t>
+          <t>IA — Sélection, formation, sécurité et pilotage</t>
         </is>
       </c>
       <c r="C25" s="11" t="n"/>
       <c r="D25" s="22" t="n"/>
       <c r="E25" s="22" t="n"/>
       <c r="F25" s="11" t="n"/>
-      <c r="G25" s="11" t="n"/>
-      <c r="H25" s="11" t="n"/>
-      <c r="I25" s="11" t="n"/>
-      <c r="J25" s="11" t="n"/>
+      <c r="G25" s="11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H25" s="11" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="I25" s="11" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="J25" s="11" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="K25" s="57" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L25" s="11" t="inlineStr">
@@ -1709,7 +1725,11 @@
           <t>C</t>
         </is>
       </c>
-      <c r="O25" s="11" t="n"/>
+      <c r="O25" s="11" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="P25" s="13" t="n"/>
     </row>
     <row r="26" ht="14.25" customHeight="1" s="55">
@@ -1720,20 +1740,28 @@
       </c>
       <c r="B26" s="28" t="inlineStr">
         <is>
-          <t xml:space="preserve">[FORMATION] </t>
+          <t>[FORMATION] OpenCode &amp; IA — État de l'art et prise en main</t>
         </is>
       </c>
       <c r="C26" s="11" t="n"/>
       <c r="D26" s="22" t="n"/>
       <c r="E26" s="22" t="n"/>
       <c r="F26" s="11" t="n"/>
-      <c r="G26" s="11" t="n"/>
-      <c r="H26" s="11" t="n"/>
+      <c r="G26" s="11" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="H26" s="11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="I26" s="11" t="n"/>
       <c r="J26" s="11" t="n"/>
       <c r="K26" s="57" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L26" s="11" t="inlineStr">
@@ -1751,7 +1779,11 @@
           <t>C</t>
         </is>
       </c>
-      <c r="O26" s="11" t="n"/>
+      <c r="O26" s="11" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="P26" s="13" t="n"/>
     </row>
     <row r="27" ht="14.25" customHeight="1" s="55">
@@ -1762,7 +1794,7 @@
       </c>
       <c r="B27" s="29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Formation IA </t>
+          <t>Formation IA : concepts de base des LLM, compréhension des tokens et du contexte</t>
         </is>
       </c>
       <c r="C27" s="11" t="n"/>
@@ -1817,125 +1849,101 @@
       <c r="P27" s="13" t="n"/>
     </row>
     <row r="28" ht="14.25" customHeight="1" s="55">
-      <c r="A28" s="28" t="inlineStr">
+      <c r="A28" s="0" t="inlineStr">
+        <is>
+          <t>T2.0.2</t>
+        </is>
+      </c>
+      <c r="B28" s="0" t="inlineStr">
+        <is>
+          <t>État de l'art des LLM pour l'extraction et l'analyse de données industrielles</t>
+        </is>
+      </c>
+      <c r="G28" s="0" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="K28" s="0" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L28" s="0" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="O28" s="0" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="14.25" customHeight="1" s="55">
+      <c r="A29" s="0" t="inlineStr">
+        <is>
+          <t>T2.0.3</t>
+        </is>
+      </c>
+      <c r="B29" s="0" t="inlineStr">
+        <is>
+          <t>Formation OpenCode avancée : modification de code, interrogation BDD, génération de scripts</t>
+        </is>
+      </c>
+      <c r="G29" s="0" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="H29" s="0" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K29" s="0" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="O29" s="0" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="14.25" customHeight="1" s="55">
+      <c r="A30" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">T2.1 </t>
         </is>
       </c>
-      <c r="B28" s="28" t="inlineStr">
+      <c r="B30" s="28" t="inlineStr">
         <is>
           <t>Sélection et Benchmark de l'IA</t>
         </is>
       </c>
-      <c r="C28" s="11" t="n"/>
-      <c r="D28" s="11" t="n"/>
-      <c r="E28" s="11" t="n"/>
-      <c r="F28" s="11" t="n"/>
-      <c r="G28" s="11" t="n"/>
-      <c r="H28" s="11" t="n"/>
-      <c r="I28" s="11" t="n"/>
-      <c r="J28" s="11" t="n"/>
-      <c r="K28" s="57" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="L28" s="11" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="M28" s="11" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="N28" s="11" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="O28" s="11" t="n"/>
-      <c r="P28" s="13" t="n"/>
-    </row>
-    <row r="29" ht="14.25" customHeight="1" s="55">
-      <c r="A29" s="29" t="inlineStr">
-        <is>
-          <t>T2.1.1</t>
-        </is>
-      </c>
-      <c r="B29" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Veille et présélection des modèles LLM locaux</t>
-        </is>
-      </c>
-      <c r="C29" s="58" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D29" s="11" t="n"/>
-      <c r="E29" s="11" t="n"/>
-      <c r="F29" s="11" t="n"/>
-      <c r="G29" s="58" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="H29" s="11" t="n"/>
-      <c r="I29" s="11" t="n"/>
-      <c r="J29" s="11" t="n"/>
-      <c r="K29" s="62" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="L29" s="11" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="M29" s="11" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="N29" s="11" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="O29" s="11" t="n"/>
-      <c r="P29" s="13" t="n"/>
-    </row>
-    <row r="30" ht="14.25" customHeight="1" s="55">
-      <c r="A30" s="29" t="inlineStr">
-        <is>
-          <t>T2.1.2</t>
-        </is>
-      </c>
-      <c r="B30" s="29" t="inlineStr">
-        <is>
-          <t>Test de compatibilité matérielle</t>
-        </is>
-      </c>
       <c r="C30" s="11" t="n"/>
-      <c r="D30" s="58" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
+      <c r="D30" s="11" t="n"/>
       <c r="E30" s="11" t="n"/>
       <c r="F30" s="11" t="n"/>
-      <c r="G30" s="11" t="n"/>
-      <c r="H30" s="58" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="I30" s="11" t="n"/>
+      <c r="G30" s="11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H30" s="11" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="I30" s="11" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="J30" s="11" t="n"/>
-      <c r="K30" s="62" t="inlineStr">
+      <c r="K30" s="57" t="inlineStr">
         <is>
           <t>R</t>
         </is>
@@ -1961,28 +1969,28 @@
     <row r="31" ht="14.25" customHeight="1" s="55">
       <c r="A31" s="29" t="inlineStr">
         <is>
-          <t xml:space="preserve">T2.1.3 </t>
+          <t>T2.1.1</t>
         </is>
       </c>
       <c r="B31" s="29" t="inlineStr">
         <is>
-          <t>Benchmark de performance</t>
-        </is>
-      </c>
-      <c r="C31" s="11" t="n"/>
+          <t xml:space="preserve"> Veille et présélection des modèles LLM locaux</t>
+        </is>
+      </c>
+      <c r="C31" s="58" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="D31" s="11" t="n"/>
-      <c r="E31" s="58" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
+      <c r="E31" s="11" t="n"/>
       <c r="F31" s="11" t="n"/>
-      <c r="G31" s="11" t="n"/>
-      <c r="H31" s="58" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+      <c r="G31" s="58" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="H31" s="11" t="n"/>
       <c r="I31" s="11" t="n"/>
       <c r="J31" s="11" t="n"/>
       <c r="K31" s="62" t="inlineStr">
@@ -2005,28 +2013,32 @@
           <t>C</t>
         </is>
       </c>
-      <c r="O31" s="11" t="n"/>
+      <c r="O31" s="11" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="P31" s="13" t="n"/>
     </row>
     <row r="32" ht="14.25" customHeight="1" s="55">
       <c r="A32" s="29" t="inlineStr">
         <is>
-          <t>T2.1.4</t>
+          <t>T2.1.2</t>
         </is>
       </c>
       <c r="B32" s="29" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Évaluation de la pertinence "Zero-Shot"</t>
+          <t>Test de compatibilité matérielle</t>
         </is>
       </c>
       <c r="C32" s="11" t="n"/>
-      <c r="D32" s="11" t="n"/>
+      <c r="D32" s="58" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="E32" s="11" t="n"/>
-      <c r="F32" s="58" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
+      <c r="F32" s="11" t="n"/>
       <c r="G32" s="11" t="n"/>
       <c r="H32" s="58" t="inlineStr">
         <is>
@@ -2055,30 +2067,38 @@
           <t>C</t>
         </is>
       </c>
-      <c r="O32" s="11" t="n"/>
+      <c r="O32" s="11" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="P32" s="13" t="n"/>
     </row>
     <row r="33" ht="14.25" customHeight="1" s="55">
       <c r="A33" s="29" t="inlineStr">
         <is>
-          <t xml:space="preserve">T2.1.5 </t>
+          <t xml:space="preserve">T2.1.3 </t>
         </is>
       </c>
       <c r="B33" s="29" t="inlineStr">
         <is>
-          <t>Analyse du compromis Précision/Poids</t>
+          <t>Benchmark de performance</t>
         </is>
       </c>
       <c r="C33" s="11" t="n"/>
       <c r="D33" s="11" t="n"/>
-      <c r="E33" s="11" t="n"/>
+      <c r="E33" s="58" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="F33" s="11" t="n"/>
-      <c r="G33" s="58" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="H33" s="11" t="n"/>
+      <c r="G33" s="11" t="n"/>
+      <c r="H33" s="58" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="I33" s="11" t="n"/>
       <c r="J33" s="11" t="n"/>
       <c r="K33" s="62" t="inlineStr">
@@ -2101,48 +2121,40 @@
           <t>C</t>
         </is>
       </c>
-      <c r="O33" s="11" t="n"/>
+      <c r="O33" s="11" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="P33" s="13" t="n"/>
     </row>
     <row r="34" ht="14.25" customHeight="1" s="55">
       <c r="A34" s="29" t="inlineStr">
         <is>
-          <t xml:space="preserve">T2.1.6 </t>
+          <t>T2.1.4</t>
         </is>
       </c>
       <c r="B34" s="29" t="inlineStr">
         <is>
-          <t>Rédaction de la note de choix technique</t>
-        </is>
-      </c>
-      <c r="C34" s="11" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
+          <t xml:space="preserve"> Évaluation de la pertinence "Zero-Shot"</t>
+        </is>
+      </c>
+      <c r="C34" s="11" t="n"/>
       <c r="D34" s="11" t="n"/>
       <c r="E34" s="11" t="n"/>
-      <c r="F34" s="11" t="n"/>
-      <c r="G34" s="58" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+      <c r="F34" s="58" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G34" s="11" t="n"/>
       <c r="H34" s="58" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="I34" s="11" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="J34" s="11" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="I34" s="11" t="n"/>
+      <c r="J34" s="11" t="n"/>
       <c r="K34" s="62" t="inlineStr">
         <is>
           <t>R</t>
@@ -2163,35 +2175,43 @@
           <t>C</t>
         </is>
       </c>
-      <c r="O34" s="11" t="n"/>
-      <c r="P34" s="11" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
+      <c r="O34" s="11" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P34" s="13" t="n"/>
     </row>
     <row r="35" ht="14.25" customHeight="1" s="55">
-      <c r="A35" s="28" t="inlineStr">
-        <is>
-          <t>T2.2</t>
-        </is>
-      </c>
-      <c r="B35" s="28" t="inlineStr">
-        <is>
-          <t>Description précise des paramètres de sortie</t>
+      <c r="A35" s="29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">T2.1.5 </t>
+        </is>
+      </c>
+      <c r="B35" s="29" t="inlineStr">
+        <is>
+          <t>Analyse du compromis Précision/Poids</t>
         </is>
       </c>
       <c r="C35" s="11" t="n"/>
       <c r="D35" s="11" t="n"/>
       <c r="E35" s="11" t="n"/>
       <c r="F35" s="11" t="n"/>
-      <c r="G35" s="11" t="n"/>
-      <c r="H35" s="19" t="n"/>
-      <c r="I35" s="11" t="n"/>
+      <c r="G35" s="58" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H35" s="11" t="n"/>
+      <c r="I35" s="11" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="J35" s="11" t="n"/>
-      <c r="K35" s="57" t="inlineStr">
-        <is>
-          <t>C</t>
+      <c r="K35" s="62" t="inlineStr">
+        <is>
+          <t>R</t>
         </is>
       </c>
       <c r="L35" s="11" t="inlineStr">
@@ -2209,35 +2229,55 @@
           <t>C</t>
         </is>
       </c>
-      <c r="O35" s="11" t="n"/>
+      <c r="O35" s="11" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="P35" s="13" t="n"/>
     </row>
     <row r="36" ht="14.25" customHeight="1" s="55">
       <c r="A36" s="29" t="inlineStr">
         <is>
-          <t>T2.2.1</t>
+          <t xml:space="preserve">T2.1.6 </t>
         </is>
       </c>
       <c r="B36" s="29" t="inlineStr">
         <is>
-          <t>Inventaire exhaustif des champs</t>
-        </is>
-      </c>
-      <c r="C36" s="11" t="n"/>
+          <t>Rédaction de la note de choix technique</t>
+        </is>
+      </c>
+      <c r="C36" s="11" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
       <c r="D36" s="11" t="n"/>
       <c r="E36" s="11" t="n"/>
       <c r="F36" s="11" t="n"/>
-      <c r="G36" s="11" t="n"/>
-      <c r="H36" s="11" t="n"/>
-      <c r="I36" s="58" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="J36" s="11" t="n"/>
-      <c r="K36" s="57" t="inlineStr">
-        <is>
-          <t>C</t>
+      <c r="G36" s="58" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="H36" s="58" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I36" s="11" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="J36" s="11" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="K36" s="62" t="inlineStr">
+        <is>
+          <t>R</t>
         </is>
       </c>
       <c r="L36" s="11" t="inlineStr">
@@ -2255,190 +2295,141 @@
           <t>C</t>
         </is>
       </c>
-      <c r="O36" s="11" t="n"/>
+      <c r="O36" s="11" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="P36" s="11" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>I</t>
         </is>
       </c>
     </row>
     <row r="37" ht="14.25" customHeight="1" s="55">
-      <c r="A37" s="29" t="inlineStr">
-        <is>
-          <t>T2.2.2</t>
-        </is>
-      </c>
-      <c r="B37" s="29" t="inlineStr">
-        <is>
-          <t>Rédaction du dictionnaire des contraintes</t>
-        </is>
-      </c>
-      <c r="C37" s="11" t="n"/>
-      <c r="D37" s="11" t="n"/>
-      <c r="E37" s="11" t="n"/>
-      <c r="F37" s="11" t="n"/>
-      <c r="G37" s="11" t="n"/>
-      <c r="H37" s="11" t="n"/>
-      <c r="I37" s="58" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="J37" s="58" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="K37" s="57" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="L37" s="11" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="M37" s="11" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="N37" s="11" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="O37" s="11" t="n"/>
-      <c r="P37" s="13" t="n"/>
+      <c r="A37" s="0" t="inlineStr">
+        <is>
+          <t>T2.1.7</t>
+        </is>
+      </c>
+      <c r="B37" s="0" t="inlineStr">
+        <is>
+          <t>Benchmark modèles locaux Ollama : Llama 3, Mistral, Qwen 2.5, DeepSeek, Phi-4</t>
+        </is>
+      </c>
+      <c r="G37" s="0" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I37" s="0" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="K37" s="0" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="O37" s="0" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="14.25" customHeight="1" s="55">
-      <c r="A38" s="31" t="inlineStr">
-        <is>
-          <t>T2.2.3</t>
-        </is>
-      </c>
-      <c r="B38" s="31" t="inlineStr">
-        <is>
-          <t>Modélisation JSON</t>
-        </is>
-      </c>
-      <c r="C38" s="11" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="D38" s="11" t="n"/>
-      <c r="E38" s="11" t="n"/>
-      <c r="F38" s="11" t="n"/>
-      <c r="G38" s="11" t="n"/>
-      <c r="H38" s="11" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="I38" s="11" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="J38" s="58" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="K38" s="62" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="L38" s="11" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="M38" s="11" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="N38" s="11" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="O38" s="11" t="n"/>
-      <c r="P38" s="13" t="n"/>
+      <c r="A38" s="0" t="inlineStr">
+        <is>
+          <t>T2.1.8</t>
+        </is>
+      </c>
+      <c r="B38" s="0" t="inlineStr">
+        <is>
+          <t>Analyse coût/efficacité : gratuit (local) vs API payante vs modèle local quantifié</t>
+        </is>
+      </c>
+      <c r="G38" s="0" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="J38" s="0" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K38" s="0" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="L38" s="0" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="O38" s="0" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="14.25" customHeight="1" s="55">
-      <c r="A39" s="28" t="inlineStr">
-        <is>
-          <t>T2.3</t>
-        </is>
-      </c>
-      <c r="B39" s="28" t="inlineStr">
-        <is>
-          <t>Préparation du dataset</t>
-        </is>
-      </c>
-      <c r="C39" s="11" t="n"/>
-      <c r="D39" s="11" t="n"/>
-      <c r="E39" s="11" t="n"/>
-      <c r="F39" s="11" t="n"/>
-      <c r="G39" s="11" t="n"/>
-      <c r="H39" s="11" t="n"/>
-      <c r="I39" s="11" t="n"/>
-      <c r="J39" s="11" t="n"/>
-      <c r="K39" s="57" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="L39" s="11" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="M39" s="11" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="N39" s="11" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="O39" s="11" t="n"/>
-      <c r="P39" s="13" t="n"/>
+      <c r="A39" s="0" t="inlineStr">
+        <is>
+          <t>T2.1.9</t>
+        </is>
+      </c>
+      <c r="B39" s="0" t="inlineStr">
+        <is>
+          <t>Analyse de sécurité : risques API externes, gestion des clés, préférence modèle local</t>
+        </is>
+      </c>
+      <c r="J39" s="0" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="K39" s="0" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L39" s="0" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="N39" s="0" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="14.25" customHeight="1" s="55">
-      <c r="A40" s="29" t="inlineStr">
-        <is>
-          <t>T2.3.1</t>
-        </is>
-      </c>
-      <c r="B40" s="29" t="inlineStr">
-        <is>
-          <t>Préparation d'exemples</t>
-        </is>
-      </c>
-      <c r="C40" s="58" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
+      <c r="A40" s="28" t="inlineStr">
+        <is>
+          <t>T2.2</t>
+        </is>
+      </c>
+      <c r="B40" s="28" t="inlineStr">
+        <is>
+          <t>Définition du schéma de sortie et règles de sécurité</t>
+        </is>
+      </c>
+      <c r="C40" s="11" t="n"/>
       <c r="D40" s="11" t="n"/>
       <c r="E40" s="11" t="n"/>
       <c r="F40" s="11" t="n"/>
       <c r="G40" s="11" t="n"/>
-      <c r="H40" s="11" t="n"/>
-      <c r="I40" s="11" t="n"/>
-      <c r="J40" s="58" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+      <c r="H40" s="19" t="n"/>
+      <c r="I40" s="11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J40" s="11" t="n"/>
       <c r="K40" s="57" t="inlineStr">
         <is>
           <t>C</t>
@@ -2459,32 +2450,40 @@
           <t>C</t>
         </is>
       </c>
-      <c r="O40" s="11" t="n"/>
-      <c r="P40" s="13" t="n"/>
+      <c r="O40" s="11" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P40" s="13" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="14.25" customHeight="1" s="55">
       <c r="A41" s="29" t="inlineStr">
         <is>
-          <t>T2.3.2</t>
+          <t>T2.2.1</t>
         </is>
       </c>
       <c r="B41" s="29" t="inlineStr">
         <is>
-          <t>Gestion des cas limite</t>
+          <t>Inventaire exhaustif des champs</t>
         </is>
       </c>
       <c r="C41" s="11" t="n"/>
-      <c r="D41" s="58" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
+      <c r="D41" s="11" t="n"/>
       <c r="E41" s="11" t="n"/>
       <c r="F41" s="11" t="n"/>
       <c r="G41" s="11" t="n"/>
       <c r="H41" s="11" t="n"/>
-      <c r="I41" s="11" t="n"/>
-      <c r="J41" s="58" t="inlineStr">
+      <c r="I41" s="58" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J41" s="11" t="inlineStr">
         <is>
           <t>R</t>
         </is>
@@ -2509,40 +2508,44 @@
           <t>C</t>
         </is>
       </c>
-      <c r="O41" s="11" t="n"/>
-      <c r="P41" s="13" t="n"/>
+      <c r="O41" s="11" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P41" s="11" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="14.25" customHeight="1" s="55">
       <c r="A42" s="29" t="inlineStr">
         <is>
-          <t>T2.3.3</t>
+          <t>T2.2.2</t>
         </is>
       </c>
       <c r="B42" s="29" t="inlineStr">
         <is>
-          <t>Anonymisation et Sécurité</t>
-        </is>
-      </c>
-      <c r="C42" s="11" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
+          <t>Rédaction du dictionnaire des contraintes</t>
+        </is>
+      </c>
+      <c r="C42" s="11" t="n"/>
       <c r="D42" s="11" t="n"/>
-      <c r="E42" s="58" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
+      <c r="E42" s="11" t="n"/>
       <c r="F42" s="11" t="n"/>
       <c r="G42" s="11" t="n"/>
       <c r="H42" s="11" t="n"/>
       <c r="I42" s="58" t="inlineStr">
         <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="J42" s="11" t="n"/>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J42" s="58" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="K42" s="57" t="inlineStr">
         <is>
           <t>C</t>
@@ -2563,31 +2566,51 @@
           <t>C</t>
         </is>
       </c>
-      <c r="O42" s="11" t="n"/>
+      <c r="O42" s="11" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="P42" s="13" t="n"/>
     </row>
     <row r="43" ht="14.25" customHeight="1" s="55">
-      <c r="A43" s="28" t="inlineStr">
-        <is>
-          <t>T2.4</t>
-        </is>
-      </c>
-      <c r="B43" s="28" t="inlineStr">
-        <is>
-          <t>Entraînement de l'IA</t>
-        </is>
-      </c>
-      <c r="C43" s="11" t="n"/>
+      <c r="A43" s="31" t="inlineStr">
+        <is>
+          <t>T2.2.3</t>
+        </is>
+      </c>
+      <c r="B43" s="31" t="inlineStr">
+        <is>
+          <t>Modélisation JSON</t>
+        </is>
+      </c>
+      <c r="C43" s="11" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
       <c r="D43" s="11" t="n"/>
       <c r="E43" s="11" t="n"/>
       <c r="F43" s="11" t="n"/>
       <c r="G43" s="11" t="n"/>
-      <c r="H43" s="11" t="n"/>
-      <c r="I43" s="11" t="n"/>
-      <c r="J43" s="11" t="n"/>
-      <c r="K43" s="57" t="inlineStr">
-        <is>
-          <t>C</t>
+      <c r="H43" s="11" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="I43" s="11" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="J43" s="58" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="K43" s="62" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
       <c r="L43" s="11" t="inlineStr">
@@ -2609,30 +2632,26 @@
       <c r="P43" s="13" t="n"/>
     </row>
     <row r="44" ht="14.25" customHeight="1" s="55">
-      <c r="A44" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">T2.4.1 </t>
-        </is>
-      </c>
-      <c r="B44" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Configuration de l'environnement local</t>
+      <c r="A44" s="28" t="inlineStr">
+        <is>
+          <t>T2.3</t>
+        </is>
+      </c>
+      <c r="B44" s="28" t="inlineStr">
+        <is>
+          <t>Préparation du dataset</t>
         </is>
       </c>
       <c r="C44" s="11" t="n"/>
       <c r="D44" s="11" t="n"/>
       <c r="E44" s="11" t="n"/>
-      <c r="F44" s="58" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="G44" s="58" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="H44" s="11" t="n"/>
+      <c r="F44" s="11" t="n"/>
+      <c r="G44" s="11" t="n"/>
+      <c r="H44" s="11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="I44" s="11" t="n"/>
       <c r="J44" s="11" t="n"/>
       <c r="K44" s="57" t="inlineStr">
@@ -2655,36 +2674,40 @@
           <t>C</t>
         </is>
       </c>
-      <c r="O44" s="11" t="n"/>
+      <c r="O44" s="11" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="P44" s="13" t="n"/>
     </row>
     <row r="45" ht="14.25" customHeight="1" s="55">
       <c r="A45" s="29" t="inlineStr">
         <is>
-          <t>T2.4.2</t>
+          <t>T2.3.1</t>
         </is>
       </c>
       <c r="B45" s="29" t="inlineStr">
         <is>
-          <t>Itérations de Prompting</t>
-        </is>
-      </c>
-      <c r="C45" s="11" t="n"/>
+          <t>Préparation d'exemples</t>
+        </is>
+      </c>
+      <c r="C45" s="58" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="D45" s="11" t="n"/>
       <c r="E45" s="11" t="n"/>
       <c r="F45" s="11" t="n"/>
-      <c r="G45" s="58" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="H45" s="58" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+      <c r="G45" s="11" t="n"/>
+      <c r="H45" s="11" t="n"/>
       <c r="I45" s="11" t="n"/>
-      <c r="J45" s="11" t="n"/>
+      <c r="J45" s="58" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="K45" s="57" t="inlineStr">
         <is>
           <t>C</t>
@@ -2711,34 +2734,30 @@
     <row r="46" ht="14.25" customHeight="1" s="55">
       <c r="A46" s="29" t="inlineStr">
         <is>
-          <t>T2.4.3</t>
+          <t>T2.3.2</t>
         </is>
       </c>
       <c r="B46" s="29" t="inlineStr">
         <is>
-          <t>Gestion de la "Fenêtre de Contexte"</t>
-        </is>
-      </c>
-      <c r="C46" s="11" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="D46" s="11" t="n"/>
+          <t>Gestion des cas limite</t>
+        </is>
+      </c>
+      <c r="C46" s="11" t="n"/>
+      <c r="D46" s="58" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="E46" s="11" t="n"/>
       <c r="F46" s="11" t="n"/>
       <c r="G46" s="11" t="n"/>
-      <c r="H46" s="58" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="I46" s="58" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="J46" s="11" t="n"/>
+      <c r="H46" s="11" t="n"/>
+      <c r="I46" s="11" t="n"/>
+      <c r="J46" s="58" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="K46" s="57" t="inlineStr">
         <is>
           <t>C</t>
@@ -2763,23 +2782,39 @@
       <c r="P46" s="13" t="n"/>
     </row>
     <row r="47" ht="14.25" customHeight="1" s="55">
-      <c r="A47" s="28" t="inlineStr">
-        <is>
-          <t>T2.5</t>
-        </is>
-      </c>
-      <c r="B47" s="28" t="inlineStr">
-        <is>
-          <t>Processus de validation</t>
-        </is>
-      </c>
-      <c r="C47" s="11" t="n"/>
+      <c r="A47" s="29" t="inlineStr">
+        <is>
+          <t>T2.3.3</t>
+        </is>
+      </c>
+      <c r="B47" s="29" t="inlineStr">
+        <is>
+          <t>Anonymisation et Sécurité</t>
+        </is>
+      </c>
+      <c r="C47" s="11" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
       <c r="D47" s="11" t="n"/>
-      <c r="E47" s="11" t="n"/>
+      <c r="E47" s="58" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="F47" s="11" t="n"/>
       <c r="G47" s="11" t="n"/>
-      <c r="H47" s="11" t="n"/>
-      <c r="I47" s="11" t="n"/>
+      <c r="H47" s="11" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="I47" s="58" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="J47" s="11" t="n"/>
       <c r="K47" s="57" t="inlineStr">
         <is>
@@ -2805,32 +2840,28 @@
       <c r="P47" s="13" t="n"/>
     </row>
     <row r="48" ht="14.25" customHeight="1" s="55">
-      <c r="A48" s="29" t="inlineStr">
-        <is>
-          <t>T2.5.1</t>
-        </is>
-      </c>
-      <c r="B48" s="29" t="inlineStr">
-        <is>
-          <t>Test de montée en charge</t>
+      <c r="A48" s="28" t="inlineStr">
+        <is>
+          <t>T2.4</t>
+        </is>
+      </c>
+      <c r="B48" s="28" t="inlineStr">
+        <is>
+          <t>Entraînement de l'IA</t>
         </is>
       </c>
       <c r="C48" s="11" t="n"/>
       <c r="D48" s="11" t="n"/>
       <c r="E48" s="11" t="n"/>
       <c r="F48" s="11" t="n"/>
-      <c r="G48" s="11" t="n"/>
+      <c r="G48" s="11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="H48" s="11" t="n"/>
-      <c r="I48" s="58" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="J48" s="58" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+      <c r="I48" s="11" t="n"/>
+      <c r="J48" s="11" t="n"/>
       <c r="K48" s="57" t="inlineStr">
         <is>
           <t>C</t>
@@ -2851,32 +2882,40 @@
           <t>C</t>
         </is>
       </c>
-      <c r="O48" s="11" t="n"/>
+      <c r="O48" s="11" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="P48" s="13" t="n"/>
     </row>
     <row r="49" ht="14.25" customHeight="1" s="55">
       <c r="A49" s="29" t="inlineStr">
         <is>
-          <t>T2.5.2</t>
+          <t xml:space="preserve">T2.4.1 </t>
         </is>
       </c>
       <c r="B49" s="29" t="inlineStr">
         <is>
-          <t>Calcul du taux de succès</t>
+          <t xml:space="preserve"> Configuration de l'environnement local</t>
         </is>
       </c>
       <c r="C49" s="11" t="n"/>
       <c r="D49" s="11" t="n"/>
       <c r="E49" s="11" t="n"/>
-      <c r="F49" s="11" t="n"/>
-      <c r="G49" s="11" t="n"/>
+      <c r="F49" s="58" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G49" s="58" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="H49" s="11" t="n"/>
       <c r="I49" s="11" t="n"/>
-      <c r="J49" s="58" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
+      <c r="J49" s="11" t="n"/>
       <c r="K49" s="57" t="inlineStr">
         <is>
           <t>C</t>
@@ -2903,41 +2942,33 @@
     <row r="50" ht="14.25" customHeight="1" s="55">
       <c r="A50" s="29" t="inlineStr">
         <is>
-          <t>T2.5.3</t>
+          <t>T2.4.2</t>
         </is>
       </c>
       <c r="B50" s="29" t="inlineStr">
         <is>
-          <t>Analyse des erreurs</t>
-        </is>
-      </c>
-      <c r="C50" s="11" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
+          <t>Itérations de Prompting</t>
+        </is>
+      </c>
+      <c r="C50" s="11" t="n"/>
       <c r="D50" s="11" t="n"/>
       <c r="E50" s="11" t="n"/>
       <c r="F50" s="11" t="n"/>
-      <c r="G50" s="11" t="n"/>
-      <c r="H50" s="11" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="I50" s="11" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="J50" s="58" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="K50" s="62" t="inlineStr">
-        <is>
-          <t>A</t>
+      <c r="G50" s="58" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H50" s="58" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="I50" s="11" t="n"/>
+      <c r="J50" s="11" t="n"/>
+      <c r="K50" s="57" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
       <c r="L50" s="11" t="inlineStr">
@@ -2959,26 +2990,45 @@
       <c r="P50" s="13" t="n"/>
     </row>
     <row r="51" ht="19.5" customHeight="1" s="55">
-      <c r="A51" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">T3
-</t>
-        </is>
-      </c>
-      <c r="B51" s="33" t="inlineStr">
-        <is>
-          <t>Prototype du Scraper</t>
-        </is>
-      </c>
-      <c r="C51" s="11" t="n"/>
-      <c r="D51" s="22" t="n"/>
-      <c r="E51" s="22" t="n"/>
+      <c r="A51" s="29" t="inlineStr">
+        <is>
+          <t>T2.4.3</t>
+        </is>
+      </c>
+      <c r="B51" s="29" t="inlineStr">
+        <is>
+          <t>Gestion de la "Fenêtre de Contexte"</t>
+        </is>
+      </c>
+      <c r="C51" s="11" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="D51" s="11" t="n"/>
+      <c r="E51" s="11" t="n"/>
       <c r="F51" s="11" t="n"/>
       <c r="G51" s="11" t="n"/>
-      <c r="H51" s="11" t="n"/>
-      <c r="I51" s="11" t="n"/>
-      <c r="J51" s="11" t="n"/>
-      <c r="K51" s="57" t="n"/>
+      <c r="H51" s="58" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I51" s="58" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="J51" s="11" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="K51" s="57" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="L51" s="11" t="inlineStr">
         <is>
           <t>C</t>
@@ -2998,25 +3048,33 @@
       <c r="P51" s="13" t="n"/>
     </row>
     <row r="52" ht="14.25" customHeight="1" s="55">
-      <c r="A52" s="34" t="inlineStr">
-        <is>
-          <t>T3.0</t>
-        </is>
-      </c>
-      <c r="B52" s="34" t="inlineStr">
-        <is>
-          <t>[FORMATION] scraping</t>
-        </is>
-      </c>
-      <c r="C52" s="22" t="n"/>
-      <c r="D52" s="22" t="n"/>
-      <c r="E52" s="22" t="n"/>
+      <c r="A52" s="28" t="inlineStr">
+        <is>
+          <t>T2.5</t>
+        </is>
+      </c>
+      <c r="B52" s="28" t="inlineStr">
+        <is>
+          <t>Processus de validation</t>
+        </is>
+      </c>
+      <c r="C52" s="11" t="n"/>
+      <c r="D52" s="11" t="n"/>
+      <c r="E52" s="11" t="n"/>
       <c r="F52" s="11" t="n"/>
       <c r="G52" s="11" t="n"/>
       <c r="H52" s="11" t="n"/>
       <c r="I52" s="11" t="n"/>
-      <c r="J52" s="11" t="n"/>
-      <c r="K52" s="57" t="n"/>
+      <c r="J52" s="11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K52" s="57" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="L52" s="11" t="inlineStr">
         <is>
           <t>C</t>
@@ -3032,45 +3090,45 @@
           <t>C</t>
         </is>
       </c>
-      <c r="O52" s="11" t="n"/>
+      <c r="O52" s="11" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="P52" s="13" t="n"/>
     </row>
     <row r="53" ht="14.25" customHeight="1" s="55">
-      <c r="A53" s="35" t="inlineStr">
-        <is>
-          <t>T3.0.1</t>
-        </is>
-      </c>
-      <c r="B53" s="35" t="inlineStr">
-        <is>
-          <t>formation Scraping</t>
-        </is>
-      </c>
-      <c r="C53" s="58" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D53" s="58" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="E53" s="58" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="F53" s="58" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+      <c r="A53" s="29" t="inlineStr">
+        <is>
+          <t>T2.5.1</t>
+        </is>
+      </c>
+      <c r="B53" s="29" t="inlineStr">
+        <is>
+          <t>Test de montée en charge</t>
+        </is>
+      </c>
+      <c r="C53" s="11" t="n"/>
+      <c r="D53" s="11" t="n"/>
+      <c r="E53" s="11" t="n"/>
+      <c r="F53" s="11" t="n"/>
       <c r="G53" s="11" t="n"/>
       <c r="H53" s="11" t="n"/>
-      <c r="I53" s="11" t="n"/>
-      <c r="J53" s="11" t="n"/>
-      <c r="K53" s="57" t="n"/>
+      <c r="I53" s="58" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J53" s="58" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="K53" s="57" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="L53" s="11" t="inlineStr">
         <is>
           <t>C</t>
@@ -3086,33 +3144,41 @@
           <t>C</t>
         </is>
       </c>
-      <c r="O53" s="11" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+      <c r="O53" s="11" t="n"/>
       <c r="P53" s="13" t="n"/>
     </row>
     <row r="54" ht="15" customHeight="1" s="55">
-      <c r="A54" s="34" t="inlineStr">
-        <is>
-          <t>T3.1</t>
-        </is>
-      </c>
-      <c r="B54" s="34" t="inlineStr">
-        <is>
-          <t>Robot Scraper</t>
-        </is>
-      </c>
-      <c r="C54" s="25" t="n"/>
-      <c r="D54" s="25" t="n"/>
-      <c r="E54" s="25" t="n"/>
+      <c r="A54" s="29" t="inlineStr">
+        <is>
+          <t>T2.5.2</t>
+        </is>
+      </c>
+      <c r="B54" s="29" t="inlineStr">
+        <is>
+          <t>Calcul du taux de succès</t>
+        </is>
+      </c>
+      <c r="C54" s="11" t="n"/>
+      <c r="D54" s="11" t="n"/>
+      <c r="E54" s="11" t="n"/>
       <c r="F54" s="11" t="n"/>
       <c r="G54" s="11" t="n"/>
       <c r="H54" s="11" t="n"/>
-      <c r="I54" s="11" t="n"/>
-      <c r="J54" s="11" t="n"/>
-      <c r="K54" s="57" t="n"/>
+      <c r="I54" s="11" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="J54" s="58" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K54" s="57" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="L54" s="11" t="inlineStr">
         <is>
           <t>C</t>
@@ -3132,37 +3198,45 @@
       <c r="P54" s="13" t="n"/>
     </row>
     <row r="55" ht="14.25" customHeight="1" s="55">
-      <c r="A55" s="35" t="inlineStr">
-        <is>
-          <t>T3.1.1</t>
-        </is>
-      </c>
-      <c r="B55" s="35" t="inlineStr">
-        <is>
-          <t>Analyse des sources et définition de la stratégie</t>
-        </is>
-      </c>
-      <c r="C55" s="11" t="n"/>
-      <c r="D55" s="58" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="E55" s="63" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="F55" s="11" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
+      <c r="A55" s="29" t="inlineStr">
+        <is>
+          <t>T2.5.3</t>
+        </is>
+      </c>
+      <c r="B55" s="29" t="inlineStr">
+        <is>
+          <t>Analyse des erreurs</t>
+        </is>
+      </c>
+      <c r="C55" s="11" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="D55" s="11" t="n"/>
+      <c r="E55" s="11" t="n"/>
+      <c r="F55" s="11" t="n"/>
       <c r="G55" s="11" t="n"/>
-      <c r="H55" s="11" t="n"/>
-      <c r="I55" s="11" t="n"/>
-      <c r="J55" s="11" t="n"/>
-      <c r="K55" s="57" t="n"/>
+      <c r="H55" s="11" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="I55" s="11" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="J55" s="58" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="K55" s="62" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="L55" s="11" t="inlineStr">
         <is>
           <t>C</t>
@@ -3178,36 +3252,29 @@
           <t>C</t>
         </is>
       </c>
-      <c r="O55" s="11" t="n"/>
+      <c r="O55" s="11" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="P55" s="13" t="n"/>
     </row>
     <row r="56" ht="11.25" customHeight="1" s="55">
-      <c r="A56" s="35" t="inlineStr">
-        <is>
-          <t>T3.1.2</t>
-        </is>
-      </c>
-      <c r="B56" s="35" t="inlineStr">
-        <is>
-          <t>choix de l'architecture du robot</t>
+      <c r="A56" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">T3
+</t>
+        </is>
+      </c>
+      <c r="B56" s="33" t="inlineStr">
+        <is>
+          <t>Prototype du Scraper</t>
         </is>
       </c>
       <c r="C56" s="11" t="n"/>
-      <c r="D56" s="63" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="E56" s="58" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="F56" s="11" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
+      <c r="D56" s="22" t="n"/>
+      <c r="E56" s="22" t="n"/>
+      <c r="F56" s="11" t="n"/>
       <c r="G56" s="11" t="n"/>
       <c r="H56" s="11" t="n"/>
       <c r="I56" s="11" t="n"/>
@@ -3232,293 +3299,202 @@
       <c r="P56" s="13" t="n"/>
     </row>
     <row r="57" ht="18" customHeight="1" s="55">
-      <c r="A57" s="35" t="inlineStr">
-        <is>
-          <t>T3.1.3</t>
-        </is>
-      </c>
-      <c r="B57" s="35" t="inlineStr">
-        <is>
-          <t>développement du moteur d'extraction</t>
-        </is>
-      </c>
-      <c r="C57" s="58" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="D57" s="58" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="E57" s="58" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="F57" s="58" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="G57" s="11" t="n"/>
-      <c r="H57" s="11" t="n"/>
-      <c r="I57" s="11" t="n"/>
-      <c r="J57" s="11" t="n"/>
-      <c r="K57" s="57" t="n"/>
-      <c r="L57" s="11" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="M57" s="11" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="N57" s="11" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="O57" s="11" t="n"/>
-      <c r="P57" s="13" t="n"/>
+      <c r="A57" s="0" t="inlineStr">
+        <is>
+          <t>T2.6</t>
+        </is>
+      </c>
+      <c r="B57" s="0" t="inlineStr">
+        <is>
+          <t>Capacités avancées de l'IA — Modification de code, dashboards et Q&amp;A</t>
+        </is>
+      </c>
+      <c r="G57" s="0" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="J57" s="0" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L57" s="0" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="O57" s="0" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
     </row>
     <row r="58" ht="18.75" customHeight="1" s="55">
-      <c r="A58" s="35" t="inlineStr">
-        <is>
-          <t>T3.1.4</t>
-        </is>
-      </c>
-      <c r="B58" s="35" t="inlineStr">
-        <is>
-          <t>Traitement des données extraites</t>
-        </is>
-      </c>
-      <c r="C58" s="11" t="n"/>
-      <c r="D58" s="11" t="n"/>
-      <c r="E58" s="11" t="n"/>
-      <c r="F58" s="58" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="G58" s="58" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="H58" s="11" t="n"/>
-      <c r="I58" s="11" t="n"/>
-      <c r="J58" s="11" t="n"/>
-      <c r="K58" s="57" t="n"/>
-      <c r="L58" s="11" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="M58" s="11" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="N58" s="11" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="O58" s="11" t="n"/>
-      <c r="P58" s="13" t="n"/>
+      <c r="A58" s="0" t="inlineStr">
+        <is>
+          <t>T2.6.1</t>
+        </is>
+      </c>
+      <c r="B58" s="0" t="inlineStr">
+        <is>
+          <t>Modification de code de scraping par prompt : l'IA modifie le code Python du scraper sur demande</t>
+        </is>
+      </c>
+      <c r="G58" s="0" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H58" s="0" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="K58" s="0" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="O58" s="0" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
     </row>
     <row r="59" ht="18.75" customHeight="1" s="55">
-      <c r="A59" s="34" t="inlineStr">
-        <is>
-          <t>T3.2</t>
-        </is>
-      </c>
-      <c r="B59" s="34" t="inlineStr">
-        <is>
-          <t>Apprentissage Robot Scraper</t>
-        </is>
-      </c>
-      <c r="C59" s="11" t="n"/>
-      <c r="D59" s="11" t="n"/>
-      <c r="E59" s="11" t="n"/>
-      <c r="F59" s="11" t="n"/>
-      <c r="G59" s="11" t="n"/>
-      <c r="H59" s="11" t="n"/>
-      <c r="I59" s="11" t="n"/>
-      <c r="J59" s="11" t="n"/>
-      <c r="K59" s="57" t="n"/>
-      <c r="L59" s="11" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="M59" s="11" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="N59" s="11" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="O59" s="11" t="n"/>
-      <c r="P59" s="13" t="n"/>
+      <c r="A59" s="0" t="inlineStr">
+        <is>
+          <t>T2.6.2</t>
+        </is>
+      </c>
+      <c r="B59" s="0" t="inlineStr">
+        <is>
+          <t>Actualisation des dashboards Power BI par prompt : visualisations, graphiques, sources</t>
+        </is>
+      </c>
+      <c r="G59" s="0" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="I59" s="0" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="K59" s="0" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
     </row>
     <row r="60" ht="18.75" customHeight="1" s="55">
-      <c r="A60" s="35" t="inlineStr">
-        <is>
-          <t>T3.2.1</t>
-        </is>
-      </c>
-      <c r="B60" s="35" t="inlineStr">
-        <is>
-          <t>Module de détection de changement de structure</t>
-        </is>
-      </c>
-      <c r="C60" s="11" t="n"/>
-      <c r="D60" s="58" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="E60" s="11" t="n"/>
-      <c r="F60" s="11" t="n"/>
-      <c r="G60" s="11" t="n"/>
-      <c r="H60" s="58" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="I60" s="11" t="n"/>
-      <c r="J60" s="11" t="n"/>
-      <c r="K60" s="57" t="n"/>
-      <c r="L60" s="11" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="M60" s="11" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="N60" s="11" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="O60" s="11" t="n"/>
-      <c r="P60" s="13" t="n"/>
+      <c r="A60" s="0" t="inlineStr">
+        <is>
+          <t>T2.6.3</t>
+        </is>
+      </c>
+      <c r="B60" s="0" t="inlineStr">
+        <is>
+          <t>Interrogation de la base de données en langage naturel (Q&amp;A → SQL)</t>
+        </is>
+      </c>
+      <c r="H60" s="0" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J60" s="0" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="K60" s="0" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="O60" s="0" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
     </row>
     <row r="61" ht="18.75" customHeight="1" s="55">
-      <c r="A61" s="35" t="inlineStr">
-        <is>
-          <t>T3.2.2</t>
-        </is>
-      </c>
-      <c r="B61" s="35" t="inlineStr">
-        <is>
-          <t>Feedback Loop pour l'auto-réparation</t>
-        </is>
-      </c>
-      <c r="C61" s="11" t="n"/>
-      <c r="D61" s="11" t="n"/>
-      <c r="E61" s="11" t="n"/>
-      <c r="F61" s="11" t="n"/>
-      <c r="G61" s="11" t="n"/>
-      <c r="H61" s="11" t="n"/>
-      <c r="I61" s="11" t="n"/>
-      <c r="J61" s="19" t="n"/>
-      <c r="K61" s="60" t="n"/>
-      <c r="L61" s="11" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="M61" s="11" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="N61" s="11" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="O61" s="11" t="n"/>
-      <c r="P61" s="13" t="n"/>
+      <c r="A61" s="0" t="inlineStr">
+        <is>
+          <t>T2.6.4</t>
+        </is>
+      </c>
+      <c r="B61" s="0" t="inlineStr">
+        <is>
+          <t>Filtrage des prompts hors-sujet : refus des demandes non liées à la collecte industrielle</t>
+        </is>
+      </c>
+      <c r="G61" s="0" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="K61" s="0" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L61" s="0" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
     </row>
     <row r="62" ht="18.75" customHeight="1" s="55">
-      <c r="A62" s="35" t="inlineStr">
-        <is>
-          <t>T3.2.3</t>
-        </is>
-      </c>
-      <c r="B62" s="35" t="inlineStr">
-        <is>
-          <t>Optimisation des performances</t>
-        </is>
-      </c>
-      <c r="C62" s="11" t="n"/>
-      <c r="D62" s="11" t="n"/>
-      <c r="E62" s="11" t="n"/>
-      <c r="F62" s="11" t="n"/>
-      <c r="G62" s="11" t="n"/>
-      <c r="H62" s="11" t="n"/>
-      <c r="I62" s="11" t="n"/>
-      <c r="J62" s="11" t="n"/>
-      <c r="K62" s="57" t="n"/>
-      <c r="L62" s="11" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="M62" s="11" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="N62" s="11" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="O62" s="11" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="P62" s="13" t="n"/>
+      <c r="A62" s="0" t="inlineStr">
+        <is>
+          <t>T2.6.5</t>
+        </is>
+      </c>
+      <c r="B62" s="0" t="inlineStr">
+        <is>
+          <t>Module de reformulation et d'explication des actions effectuées par l'IA</t>
+        </is>
+      </c>
+      <c r="G62" s="0" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="I62" s="0" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K62" s="0" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
     </row>
     <row r="63" ht="21.75" customHeight="1" s="55">
-      <c r="A63" s="37" t="inlineStr">
-        <is>
-          <t>T4</t>
-        </is>
-      </c>
-      <c r="B63" s="38" t="inlineStr">
-        <is>
-          <t>Système Auto-réparateur</t>
+      <c r="A63" s="34" t="inlineStr">
+        <is>
+          <t>T3.0</t>
+        </is>
+      </c>
+      <c r="B63" s="34" t="inlineStr">
+        <is>
+          <t>[FORMATION] scraping</t>
         </is>
       </c>
       <c r="C63" s="22" t="n"/>
-      <c r="D63" s="39" t="n"/>
-      <c r="E63" s="39" t="n"/>
+      <c r="D63" s="22" t="n"/>
+      <c r="E63" s="22" t="n"/>
       <c r="F63" s="11" t="n"/>
       <c r="G63" s="11" t="n"/>
       <c r="H63" s="11" t="n"/>
       <c r="I63" s="11" t="n"/>
       <c r="J63" s="11" t="n"/>
-      <c r="K63" s="57" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+      <c r="K63" s="57" t="n"/>
       <c r="L63" s="11" t="inlineStr">
         <is>
           <t>C</t>
@@ -3538,29 +3514,41 @@
       <c r="P63" s="13" t="n"/>
     </row>
     <row r="64" ht="14.25" customHeight="1" s="55">
-      <c r="A64" s="40" t="inlineStr">
-        <is>
-          <t>T4.1</t>
-        </is>
-      </c>
-      <c r="B64" s="40" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Ingénierie de Prompt </t>
-        </is>
-      </c>
-      <c r="C64" s="22" t="n"/>
-      <c r="D64" s="39" t="n"/>
-      <c r="E64" s="39" t="n"/>
-      <c r="F64" s="11" t="n"/>
+      <c r="A64" s="35" t="inlineStr">
+        <is>
+          <t>T3.0.1</t>
+        </is>
+      </c>
+      <c r="B64" s="35" t="inlineStr">
+        <is>
+          <t>formation Scraping</t>
+        </is>
+      </c>
+      <c r="C64" s="58" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D64" s="58" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E64" s="58" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F64" s="58" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="G64" s="11" t="n"/>
       <c r="H64" s="11" t="n"/>
       <c r="I64" s="11" t="n"/>
       <c r="J64" s="11" t="n"/>
-      <c r="K64" s="57" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+      <c r="K64" s="57" t="n"/>
       <c r="L64" s="11" t="inlineStr">
         <is>
           <t>C</t>
@@ -3576,45 +3564,33 @@
           <t>C</t>
         </is>
       </c>
-      <c r="O64" s="11" t="n"/>
+      <c r="O64" s="11" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="P64" s="13" t="n"/>
     </row>
     <row r="65" ht="14.25" customHeight="1" s="55">
-      <c r="A65" s="41" t="inlineStr">
-        <is>
-          <t>T4.1.1</t>
-        </is>
-      </c>
-      <c r="B65" s="41" t="inlineStr">
-        <is>
-          <t>Veille technique</t>
-        </is>
-      </c>
-      <c r="C65" s="22" t="n"/>
-      <c r="D65" s="11" t="n"/>
-      <c r="E65" s="11" t="n"/>
+      <c r="A65" s="34" t="inlineStr">
+        <is>
+          <t>T3.1</t>
+        </is>
+      </c>
+      <c r="B65" s="34" t="inlineStr">
+        <is>
+          <t>Robot Scraper</t>
+        </is>
+      </c>
+      <c r="C65" s="25" t="n"/>
+      <c r="D65" s="25" t="n"/>
+      <c r="E65" s="25" t="n"/>
       <c r="F65" s="11" t="n"/>
-      <c r="G65" s="58" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="H65" s="11" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="I65" s="58" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
+      <c r="G65" s="11" t="n"/>
+      <c r="H65" s="11" t="n"/>
+      <c r="I65" s="11" t="n"/>
       <c r="J65" s="11" t="n"/>
-      <c r="K65" s="57" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+      <c r="K65" s="57" t="n"/>
       <c r="L65" s="11" t="inlineStr">
         <is>
           <t>C</t>
@@ -3634,41 +3610,37 @@
       <c r="P65" s="13" t="n"/>
     </row>
     <row r="66" ht="14.25" customHeight="1" s="55">
-      <c r="A66" s="41" t="inlineStr">
-        <is>
-          <t>T4.1.2</t>
-        </is>
-      </c>
-      <c r="B66" s="41" t="inlineStr">
-        <is>
-          <t>Création du Dataset de test</t>
-        </is>
-      </c>
-      <c r="C66" s="22" t="n"/>
-      <c r="D66" s="11" t="n"/>
-      <c r="E66" s="11" t="n"/>
-      <c r="F66" s="11" t="n"/>
+      <c r="A66" s="35" t="inlineStr">
+        <is>
+          <t>T3.1.1</t>
+        </is>
+      </c>
+      <c r="B66" s="35" t="inlineStr">
+        <is>
+          <t>Analyse des sources et définition de la stratégie</t>
+        </is>
+      </c>
+      <c r="C66" s="11" t="n"/>
+      <c r="D66" s="58" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E66" s="63" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F66" s="11" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
       <c r="G66" s="11" t="n"/>
-      <c r="H66" s="58" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="I66" s="11" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="J66" s="58" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="K66" s="62" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
+      <c r="H66" s="11" t="n"/>
+      <c r="I66" s="11" t="n"/>
+      <c r="J66" s="11" t="n"/>
+      <c r="K66" s="57" t="n"/>
       <c r="L66" s="11" t="inlineStr">
         <is>
           <t>C</t>
@@ -3688,37 +3660,37 @@
       <c r="P66" s="13" t="n"/>
     </row>
     <row r="67" ht="14.25" customHeight="1" s="55">
-      <c r="A67" s="41" t="inlineStr">
-        <is>
-          <t>T4.1.3</t>
-        </is>
-      </c>
-      <c r="B67" s="41" t="inlineStr">
-        <is>
-          <t>Optimisation du "System Prompt"</t>
-        </is>
-      </c>
-      <c r="C67" s="22" t="n"/>
-      <c r="D67" s="11" t="n"/>
-      <c r="E67" s="11" t="n"/>
-      <c r="F67" s="11" t="n"/>
+      <c r="A67" s="35" t="inlineStr">
+        <is>
+          <t>T3.1.2</t>
+        </is>
+      </c>
+      <c r="B67" s="35" t="inlineStr">
+        <is>
+          <t>choix de l'architecture du robot</t>
+        </is>
+      </c>
+      <c r="C67" s="11" t="n"/>
+      <c r="D67" s="63" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E67" s="58" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F67" s="11" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
       <c r="G67" s="11" t="n"/>
-      <c r="H67" s="11" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="I67" s="58" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+      <c r="H67" s="11" t="n"/>
+      <c r="I67" s="11" t="n"/>
       <c r="J67" s="11" t="n"/>
-      <c r="K67" s="62" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
+      <c r="K67" s="57" t="n"/>
       <c r="L67" s="11" t="inlineStr">
         <is>
           <t>C</t>
@@ -3738,247 +3710,191 @@
       <c r="P67" s="13" t="n"/>
     </row>
     <row r="68" ht="14.25" customHeight="1" s="55">
-      <c r="A68" s="40" t="inlineStr">
-        <is>
-          <t>T4.2</t>
-        </is>
-      </c>
-      <c r="B68" s="40" t="inlineStr">
-        <is>
-          <t>Connexion IA/Robot</t>
-        </is>
-      </c>
-      <c r="C68" s="22" t="n"/>
-      <c r="D68" s="11" t="n"/>
-      <c r="E68" s="11" t="n"/>
-      <c r="F68" s="11" t="n"/>
+      <c r="A68" s="34" t="inlineStr">
+        <is>
+          <t>T3.2</t>
+        </is>
+      </c>
+      <c r="B68" s="34" t="inlineStr">
+        <is>
+          <t>Robustesse et adaptation du scraper</t>
+        </is>
+      </c>
+      <c r="C68" s="11" t="n"/>
+      <c r="D68" s="11" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E68" s="11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F68" s="11" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="G68" s="11" t="n"/>
       <c r="H68" s="11" t="n"/>
       <c r="I68" s="11" t="n"/>
       <c r="J68" s="11" t="n"/>
-      <c r="K68" s="62" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="L68" s="11" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="M68" s="11" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="N68" s="11" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="O68" s="11" t="n"/>
+      <c r="K68" s="57" t="n"/>
+      <c r="L68" s="11" t="n"/>
+      <c r="M68" s="11" t="n"/>
+      <c r="N68" s="11" t="n"/>
+      <c r="O68" s="11" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="P68" s="13" t="n"/>
     </row>
     <row r="69" ht="14.25" customHeight="1" s="55">
-      <c r="A69" s="41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">T4.2.1 </t>
-        </is>
-      </c>
-      <c r="B69" s="41" t="inlineStr">
-        <is>
-          <t>Module de détection d'échec</t>
-        </is>
-      </c>
-      <c r="C69" s="63" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D69" s="11" t="n"/>
+      <c r="A69" s="35" t="inlineStr">
+        <is>
+          <t>T3.2.1</t>
+        </is>
+      </c>
+      <c r="B69" s="35" t="inlineStr">
+        <is>
+          <t>Module de détection de changement de structure</t>
+        </is>
+      </c>
+      <c r="C69" s="11" t="n"/>
+      <c r="D69" s="58" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="E69" s="11" t="n"/>
       <c r="F69" s="11" t="n"/>
       <c r="G69" s="11" t="n"/>
-      <c r="H69" s="11" t="n"/>
-      <c r="I69" s="11" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="J69" s="58" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="K69" s="57" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="L69" s="11" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="M69" s="11" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="N69" s="11" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+      <c r="H69" s="58" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I69" s="11" t="n"/>
+      <c r="J69" s="11" t="n"/>
+      <c r="K69" s="57" t="n"/>
+      <c r="L69" s="11" t="n"/>
+      <c r="M69" s="11" t="n"/>
+      <c r="N69" s="11" t="n"/>
       <c r="O69" s="11" t="n"/>
       <c r="P69" s="13" t="n"/>
     </row>
     <row r="70" ht="14.25" customHeight="1" s="55">
-      <c r="A70" s="41" t="inlineStr">
-        <is>
-          <t>T4.2.2</t>
-        </is>
-      </c>
-      <c r="B70" s="41" t="inlineStr">
-        <is>
-          <t>Pipeline d'envoi HTML</t>
-        </is>
-      </c>
-      <c r="C70" s="11" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="D70" s="58" t="inlineStr">
-        <is>
-          <t>A</t>
+      <c r="A70" s="35" t="inlineStr">
+        <is>
+          <t>T3.2.2</t>
+        </is>
+      </c>
+      <c r="B70" s="35" t="inlineStr">
+        <is>
+          <t>Logging et journalisation : loggue l'erreur et passe au site suivant si structure changée</t>
+        </is>
+      </c>
+      <c r="C70" s="11" t="n"/>
+      <c r="D70" s="11" t="inlineStr">
+        <is>
+          <t>R</t>
         </is>
       </c>
       <c r="E70" s="11" t="n"/>
-      <c r="F70" s="11" t="n"/>
+      <c r="F70" s="11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="G70" s="11" t="n"/>
       <c r="H70" s="11" t="n"/>
-      <c r="I70" s="58" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="J70" s="11" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="K70" s="57" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="L70" s="11" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="M70" s="11" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="N70" s="11" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+      <c r="I70" s="11" t="n"/>
+      <c r="J70" s="19" t="n"/>
+      <c r="K70" s="60" t="n"/>
+      <c r="L70" s="11" t="n"/>
+      <c r="M70" s="11" t="n"/>
+      <c r="N70" s="11" t="n"/>
       <c r="O70" s="11" t="n"/>
       <c r="P70" s="13" t="n"/>
     </row>
     <row r="71" ht="14.25" customHeight="1" s="55">
-      <c r="A71" s="41" t="inlineStr">
-        <is>
-          <t>T4.2.3</t>
-        </is>
-      </c>
-      <c r="B71" s="41" t="inlineStr">
-        <is>
-          <t>Parseur de réponse IA</t>
-        </is>
-      </c>
-      <c r="C71" s="22" t="n"/>
+      <c r="A71" s="35" t="inlineStr">
+        <is>
+          <t>T3.2.3</t>
+        </is>
+      </c>
+      <c r="B71" s="35" t="inlineStr">
+        <is>
+          <t>Optimisation des performances</t>
+        </is>
+      </c>
+      <c r="C71" s="11" t="n"/>
       <c r="D71" s="11" t="n"/>
-      <c r="E71" s="58" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
+      <c r="E71" s="11" t="n"/>
       <c r="F71" s="11" t="n"/>
       <c r="G71" s="11" t="n"/>
       <c r="H71" s="11" t="n"/>
       <c r="I71" s="11" t="inlineStr">
         <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="J71" s="58" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="K71" s="57" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="L71" s="11" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="M71" s="11" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="N71" s="11" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="O71" s="11" t="n"/>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J71" s="11" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="K71" s="57" t="n"/>
+      <c r="L71" s="11" t="n"/>
+      <c r="M71" s="11" t="n"/>
+      <c r="N71" s="11" t="n"/>
+      <c r="O71" s="11" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="P71" s="13" t="n"/>
     </row>
     <row r="72" ht="14.25" customHeight="1" s="55">
-      <c r="A72" s="41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">T4.2.4 </t>
-        </is>
-      </c>
-      <c r="B72" s="41" t="inlineStr">
-        <is>
-          <t>Module d'injection dynamique</t>
+      <c r="A72" s="37" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="B72" s="38" t="inlineStr">
+        <is>
+          <t>Pilotage IA &amp; Controle dynamique</t>
         </is>
       </c>
       <c r="C72" s="22" t="n"/>
-      <c r="D72" s="11" t="n"/>
-      <c r="E72" s="11" t="n"/>
-      <c r="F72" s="58" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="G72" s="11" t="n"/>
-      <c r="H72" s="11" t="n"/>
-      <c r="I72" s="58" t="inlineStr">
+      <c r="D72" s="39" t="n"/>
+      <c r="E72" s="39" t="n"/>
+      <c r="F72" s="11" t="n"/>
+      <c r="G72" s="11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H72" s="11" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="I72" s="11" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
       <c r="J72" s="11" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>R</t>
         </is>
       </c>
       <c r="K72" s="57" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L72" s="11" t="inlineStr">
@@ -3996,31 +3912,43 @@
           <t>C</t>
         </is>
       </c>
-      <c r="O72" s="11" t="n"/>
+      <c r="O72" s="11" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="P72" s="13" t="n"/>
     </row>
     <row r="73" ht="14.25" customHeight="1" s="55">
       <c r="A73" s="40" t="inlineStr">
         <is>
-          <t>T4.3</t>
+          <t>T4.1</t>
         </is>
       </c>
       <c r="B73" s="40" t="inlineStr">
         <is>
-          <t>Module de Nettoyage</t>
+          <t>[FORMATION] Prompt Engineering &amp; IA Generative</t>
         </is>
       </c>
       <c r="C73" s="22" t="n"/>
-      <c r="D73" s="11" t="n"/>
-      <c r="E73" s="11" t="n"/>
+      <c r="D73" s="39" t="n"/>
+      <c r="E73" s="39" t="n"/>
       <c r="F73" s="11" t="n"/>
-      <c r="G73" s="11" t="n"/>
-      <c r="H73" s="11" t="n"/>
+      <c r="G73" s="11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H73" s="11" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="I73" s="11" t="n"/>
       <c r="J73" s="11" t="n"/>
       <c r="K73" s="57" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L73" s="11" t="inlineStr">
@@ -4038,18 +3966,22 @@
           <t>C</t>
         </is>
       </c>
-      <c r="O73" s="11" t="n"/>
+      <c r="O73" s="11" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="P73" s="13" t="n"/>
     </row>
     <row r="74" ht="14.25" customHeight="1" s="55">
       <c r="A74" s="41" t="inlineStr">
         <is>
-          <t>T4.3.1</t>
+          <t>T4.1.1</t>
         </is>
       </c>
       <c r="B74" s="41" t="inlineStr">
         <is>
-          <t>Scripts de nettoyage Regex</t>
+          <t>Formation aux techniques de prompt (Few-shot, Chain-of-Thought)</t>
         </is>
       </c>
       <c r="C74" s="22" t="n"/>
@@ -4058,19 +3990,23 @@
       <c r="F74" s="11" t="n"/>
       <c r="G74" s="58" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="H74" s="58" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="I74" s="11" t="n"/>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="H74" s="11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I74" s="58" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="J74" s="11" t="n"/>
       <c r="K74" s="57" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L74" s="11" t="inlineStr">
@@ -4094,29 +4030,41 @@
     <row r="75" ht="14.25" customHeight="1" s="55">
       <c r="A75" s="41" t="inlineStr">
         <is>
-          <t>T4.3.2</t>
+          <t>T4.1.2</t>
         </is>
       </c>
       <c r="B75" s="41" t="inlineStr">
         <is>
-          <t>Standardisation des formats</t>
+          <t>Pratique : prompts de modification de code (ajout champs, selecteurs, sources)</t>
         </is>
       </c>
       <c r="C75" s="22" t="n"/>
       <c r="D75" s="11" t="n"/>
       <c r="E75" s="11" t="n"/>
       <c r="F75" s="11" t="n"/>
-      <c r="G75" s="11" t="n"/>
+      <c r="G75" s="11" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="H75" s="58" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I75" s="11" t="n"/>
-      <c r="J75" s="11" t="n"/>
-      <c r="K75" s="57" t="inlineStr">
-        <is>
-          <t>C</t>
+      <c r="I75" s="11" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="J75" s="58" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K75" s="62" t="inlineStr">
+        <is>
+          <t>R</t>
         </is>
       </c>
       <c r="L75" s="11" t="inlineStr">
@@ -4140,37 +4088,37 @@
     <row r="76" ht="14.25" customHeight="1" s="55">
       <c r="A76" s="41" t="inlineStr">
         <is>
-          <t xml:space="preserve">T4.3.3 </t>
+          <t>T4.1.3</t>
         </is>
       </c>
       <c r="B76" s="41" t="inlineStr">
         <is>
-          <t>Dédoublonnage et Intégrité</t>
+          <t>Pratique : prompts d'interrogation de BDD (agregations, filtres, multi-criteres)</t>
         </is>
       </c>
       <c r="C76" s="22" t="n"/>
       <c r="D76" s="11" t="n"/>
       <c r="E76" s="11" t="n"/>
       <c r="F76" s="11" t="n"/>
-      <c r="G76" s="58" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+      <c r="G76" s="11" t="n"/>
       <c r="H76" s="11" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>R</t>
         </is>
       </c>
       <c r="I76" s="58" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="J76" s="11" t="n"/>
-      <c r="K76" s="57" t="inlineStr">
-        <is>
-          <t>C</t>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="J76" s="11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K76" s="62" t="inlineStr">
+        <is>
+          <t>R</t>
         </is>
       </c>
       <c r="L76" s="11" t="inlineStr">
@@ -4192,133 +4140,237 @@
       <c r="P76" s="13" t="n"/>
     </row>
     <row r="77" ht="19.5" customHeight="1" s="55">
-      <c r="A77" s="42" t="inlineStr">
-        <is>
-          <t>T5</t>
-        </is>
-      </c>
-      <c r="B77" s="43" t="inlineStr">
-        <is>
-          <t>Finalisation</t>
+      <c r="A77" s="40" t="inlineStr">
+        <is>
+          <t>T4.2</t>
+        </is>
+      </c>
+      <c r="B77" s="40" t="inlineStr">
+        <is>
+          <t>Module de modification de code par prompt</t>
         </is>
       </c>
       <c r="C77" s="22" t="n"/>
-      <c r="D77" s="39" t="n"/>
-      <c r="E77" s="39" t="n"/>
+      <c r="D77" s="11" t="n"/>
+      <c r="E77" s="11" t="n"/>
       <c r="F77" s="11" t="n"/>
-      <c r="G77" s="11" t="n"/>
-      <c r="H77" s="11" t="n"/>
-      <c r="I77" s="11" t="n"/>
+      <c r="G77" s="11" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="H77" s="11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I77" s="11" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="J77" s="11" t="n"/>
-      <c r="K77" s="57" t="n"/>
-      <c r="L77" s="11" t="n"/>
-      <c r="M77" s="11" t="n"/>
-      <c r="N77" s="11" t="n"/>
-      <c r="O77" s="11" t="n"/>
+      <c r="K77" s="62" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L77" s="11" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="M77" s="11" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="N77" s="11" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="O77" s="11" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="P77" s="13" t="n"/>
     </row>
     <row r="78" ht="14.25" customHeight="1" s="55">
-      <c r="A78" s="44" t="inlineStr">
-        <is>
-          <t>T5.1</t>
-        </is>
-      </c>
-      <c r="B78" s="44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">formation  data </t>
-        </is>
-      </c>
-      <c r="C78" s="58" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="D78" s="58" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="E78" s="58" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="F78" s="58" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="G78" s="11" t="n"/>
-      <c r="H78" s="11" t="n"/>
-      <c r="I78" s="11" t="n"/>
+      <c r="A78" s="41" t="inlineStr">
+        <is>
+          <t>T4.2.1</t>
+        </is>
+      </c>
+      <c r="B78" s="41" t="inlineStr">
+        <is>
+          <t>Interface de soumission de prompt -&gt; envoi a l'IA -&gt; recuperation reponse</t>
+        </is>
+      </c>
+      <c r="C78" s="63" t="n"/>
+      <c r="D78" s="11" t="n"/>
+      <c r="E78" s="11" t="n"/>
+      <c r="F78" s="11" t="n"/>
+      <c r="G78" s="11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H78" s="11" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="I78" s="11" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
       <c r="J78" s="58" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="K78" s="57" t="n"/>
-      <c r="L78" s="11" t="n"/>
-      <c r="M78" s="11" t="n"/>
-      <c r="N78" s="11" t="n"/>
-      <c r="O78" s="11" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="K78" s="57" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L78" s="11" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="M78" s="11" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="N78" s="11" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="O78" s="11" t="n"/>
       <c r="P78" s="13" t="n"/>
     </row>
     <row r="79" ht="14.25" customHeight="1" s="55">
-      <c r="A79" s="44" t="inlineStr">
-        <is>
-          <t>T5.2</t>
-        </is>
-      </c>
-      <c r="B79" s="44" t="inlineStr">
-        <is>
-          <t>Conception du Dashboard Power BI</t>
-        </is>
-      </c>
-      <c r="C79" s="22" t="n"/>
-      <c r="D79" s="11" t="n"/>
+      <c r="A79" s="41" t="inlineStr">
+        <is>
+          <t>T4.2.2</t>
+        </is>
+      </c>
+      <c r="B79" s="41" t="inlineStr">
+        <is>
+          <t>Analyse et validation du code genere : extraction, verification syntaxique, validation</t>
+        </is>
+      </c>
+      <c r="C79" s="11" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="D79" s="58" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="E79" s="11" t="n"/>
-      <c r="F79" s="11" t="n"/>
-      <c r="G79" s="11" t="n"/>
-      <c r="H79" s="11" t="n"/>
-      <c r="I79" s="11" t="n"/>
-      <c r="J79" s="11" t="n"/>
-      <c r="K79" s="57" t="n"/>
-      <c r="L79" s="11" t="n"/>
-      <c r="M79" s="11" t="n"/>
-      <c r="N79" s="11" t="n"/>
-      <c r="O79" s="11" t="n"/>
+      <c r="F79" s="11" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="G79" s="11" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="H79" s="11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I79" s="58" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="J79" s="11" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="K79" s="57" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L79" s="11" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="M79" s="11" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="N79" s="11" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="O79" s="11" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="P79" s="13" t="n"/>
     </row>
     <row r="80" ht="14.25" customHeight="1" s="55">
-      <c r="A80" s="45" t="inlineStr">
-        <is>
-          <t>T5.2.1</t>
-        </is>
-      </c>
-      <c r="B80" s="46" t="inlineStr">
-        <is>
-          <t>Conception de la structure du Dashboard</t>
-        </is>
-      </c>
-      <c r="C80" s="11" t="n"/>
-      <c r="D80" s="11" t="n"/>
-      <c r="E80" s="11" t="n"/>
-      <c r="F80" s="58" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="G80" s="11" t="n"/>
-      <c r="H80" s="11" t="n"/>
-      <c r="I80" s="11" t="n"/>
-      <c r="J80" s="11" t="n"/>
-      <c r="K80" s="62" t="inlineStr">
-        <is>
-          <t>A</t>
+      <c r="A80" s="41" t="inlineStr">
+        <is>
+          <t>T4.2.3</t>
+        </is>
+      </c>
+      <c r="B80" s="41" t="inlineStr">
+        <is>
+          <t>Module de test automatique : execution du nouveau code sur echantillon de test</t>
+        </is>
+      </c>
+      <c r="C80" s="22" t="n"/>
+      <c r="D80" s="11" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E80" s="58" t="n"/>
+      <c r="F80" s="11" t="n"/>
+      <c r="G80" s="11" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="H80" s="11" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="I80" s="11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J80" s="58" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="K80" s="57" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
       <c r="L80" s="11" t="inlineStr">
@@ -4326,542 +4378,846 @@
           <t>C</t>
         </is>
       </c>
-      <c r="M80" s="11" t="n"/>
-      <c r="N80" s="11" t="n"/>
+      <c r="M80" s="11" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="N80" s="11" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="O80" s="11" t="n"/>
       <c r="P80" s="13" t="n"/>
     </row>
     <row r="81" ht="14.25" customHeight="1" s="55">
-      <c r="A81" s="47" t="inlineStr">
-        <is>
-          <t>T5.2.2</t>
-        </is>
-      </c>
-      <c r="B81" s="48" t="inlineStr">
-        <is>
-          <t>Developpement des rapports et visualisations Power BI</t>
-        </is>
-      </c>
-      <c r="C81" s="58" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D81" s="11" t="n"/>
+      <c r="A81" s="41" t="inlineStr">
+        <is>
+          <t>T4.2.4</t>
+        </is>
+      </c>
+      <c r="B81" s="41" t="inlineStr">
+        <is>
+          <t>Gestion des erreurs et rollback : retour automatique a la version precedente</t>
+        </is>
+      </c>
+      <c r="C81" s="22" t="n"/>
+      <c r="D81" s="11" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="E81" s="11" t="n"/>
-      <c r="F81" s="58" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+      <c r="F81" s="58" t="n"/>
       <c r="G81" s="11" t="n"/>
-      <c r="H81" s="11" t="n"/>
-      <c r="I81" s="11" t="n"/>
-      <c r="J81" s="11" t="n"/>
-      <c r="K81" s="57" t="n"/>
-      <c r="L81" s="11" t="n"/>
-      <c r="M81" s="11" t="n"/>
-      <c r="N81" s="11" t="n"/>
+      <c r="H81" s="11" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="I81" s="58" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="J81" s="11" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="K81" s="57" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L81" s="11" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="M81" s="11" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="N81" s="11" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="O81" s="11" t="n"/>
       <c r="P81" s="13" t="n"/>
     </row>
     <row r="82" ht="14.25" customHeight="1" s="55">
-      <c r="A82" s="47" t="inlineStr">
-        <is>
-          <t>T5.2.3</t>
-        </is>
-      </c>
-      <c r="B82" s="48" t="inlineStr">
-        <is>
-          <t>Connexion donnees → Power BI (Power Query)</t>
-        </is>
-      </c>
-      <c r="C82" s="11" t="n"/>
-      <c r="D82" s="58" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
+      <c r="A82" s="40" t="inlineStr">
+        <is>
+          <t>T4.3</t>
+        </is>
+      </c>
+      <c r="B82" s="40" t="inlineStr">
+        <is>
+          <t>Module d'ajout de sources et de donnees</t>
+        </is>
+      </c>
+      <c r="C82" s="22" t="n"/>
+      <c r="D82" s="11" t="n"/>
       <c r="E82" s="11" t="n"/>
-      <c r="F82" s="58" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="G82" s="11" t="n"/>
+      <c r="F82" s="11" t="n"/>
+      <c r="G82" s="11" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="H82" s="11" t="n"/>
-      <c r="I82" s="11" t="n"/>
-      <c r="J82" s="11" t="n"/>
-      <c r="K82" s="57" t="n"/>
-      <c r="L82" s="11" t="n"/>
-      <c r="M82" s="11" t="n"/>
-      <c r="N82" s="11" t="n"/>
-      <c r="O82" s="11" t="n"/>
+      <c r="I82" s="11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J82" s="11" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="K82" s="57" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="L82" s="11" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="M82" s="11" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="N82" s="11" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="O82" s="11" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="P82" s="13" t="n"/>
     </row>
     <row r="83" ht="14.25" customHeight="1" s="55">
-      <c r="A83" s="47" t="inlineStr">
-        <is>
-          <t>T5.2.4</t>
-        </is>
-      </c>
-      <c r="B83" s="48" t="inlineStr">
-        <is>
-          <t>Ecriture des formules DAX et indicateurs calcules</t>
-        </is>
-      </c>
-      <c r="C83" s="58" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+      <c r="A83" s="41" t="inlineStr">
+        <is>
+          <t>T4.3.1</t>
+        </is>
+      </c>
+      <c r="B83" s="41" t="inlineStr">
+        <is>
+          <t>Ajout de nouveaux sites : analyse structure, generation selecteurs, integration</t>
+        </is>
+      </c>
+      <c r="C83" s="22" t="n"/>
       <c r="D83" s="11" t="n"/>
-      <c r="E83" s="58" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="F83" s="11" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="G83" s="11" t="n"/>
-      <c r="H83" s="11" t="n"/>
-      <c r="I83" s="11" t="n"/>
-      <c r="J83" s="11" t="n"/>
-      <c r="K83" s="57" t="n"/>
-      <c r="L83" s="11" t="n"/>
-      <c r="M83" s="11" t="n"/>
-      <c r="N83" s="11" t="n"/>
-      <c r="O83" s="11" t="n"/>
-      <c r="P83" s="49" t="n"/>
+      <c r="E83" s="11" t="n"/>
+      <c r="F83" s="11" t="n"/>
+      <c r="G83" s="58" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H83" s="58" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="I83" s="11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J83" s="11" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="K83" s="57" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="L83" s="11" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="M83" s="11" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="N83" s="11" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="O83" s="11" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P83" s="13" t="n"/>
     </row>
     <row r="84" ht="14.25" customHeight="1" s="55">
-      <c r="A84" s="50" t="inlineStr">
-        <is>
-          <t>T5.2.5</t>
-        </is>
-      </c>
-      <c r="B84" s="51" t="inlineStr">
-        <is>
-          <t>Validation et livraison du Dashboard</t>
-        </is>
-      </c>
-      <c r="C84" s="19" t="n"/>
-      <c r="D84" s="11" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="E84" s="11" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="F84" s="58" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="G84" s="11" t="n"/>
-      <c r="H84" s="11" t="n"/>
-      <c r="I84" s="11" t="n"/>
-      <c r="J84" s="11" t="n"/>
-      <c r="K84" s="57" t="n"/>
+      <c r="A84" s="41" t="inlineStr">
+        <is>
+          <t>T4.3.2</t>
+        </is>
+      </c>
+      <c r="B84" s="41" t="inlineStr">
+        <is>
+          <t>Ajout de nouveaux champs : adaptation BDD, modification scraper, mise a jour Power BI</t>
+        </is>
+      </c>
+      <c r="C84" s="22" t="n"/>
+      <c r="D84" s="11" t="n"/>
+      <c r="E84" s="11" t="n"/>
+      <c r="F84" s="11" t="n"/>
+      <c r="G84" s="11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H84" s="58" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="I84" s="11" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="J84" s="11" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="K84" s="57" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="L84" s="11" t="inlineStr">
         <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="M84" s="11" t="n"/>
-      <c r="N84" s="11" t="n"/>
-      <c r="O84" s="11" t="n"/>
-      <c r="P84" s="11" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="M84" s="11" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="N84" s="11" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="O84" s="11" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P84" s="13" t="n"/>
     </row>
     <row r="85" ht="14.25" customHeight="1" s="55">
-      <c r="A85" s="44" t="inlineStr">
-        <is>
-          <t>T5.3</t>
-        </is>
-      </c>
-      <c r="B85" s="44" t="inlineStr">
-        <is>
-          <t>Interface de Pilotage (Monitoring)</t>
+      <c r="A85" s="41" t="inlineStr">
+        <is>
+          <t>T4.3.3</t>
+        </is>
+      </c>
+      <c r="B85" s="41" t="inlineStr">
+        <is>
+          <t>Validation et confirmation : resume des changements avant application definitive</t>
         </is>
       </c>
       <c r="C85" s="22" t="n"/>
       <c r="D85" s="11" t="n"/>
       <c r="E85" s="11" t="n"/>
       <c r="F85" s="11" t="n"/>
-      <c r="G85" s="11" t="n"/>
-      <c r="H85" s="11" t="n"/>
-      <c r="I85" s="11" t="n"/>
-      <c r="J85" s="11" t="n"/>
-      <c r="K85" s="57" t="n"/>
-      <c r="L85" s="11" t="n"/>
-      <c r="M85" s="11" t="n"/>
-      <c r="N85" s="11" t="n"/>
+      <c r="G85" s="58" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="H85" s="11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I85" s="58" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="J85" s="11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K85" s="57" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="L85" s="11" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="M85" s="11" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="N85" s="11" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="O85" s="11" t="n"/>
-      <c r="P85" s="49" t="n"/>
+      <c r="P85" s="13" t="n"/>
     </row>
     <row r="86" ht="14.25" customHeight="1" s="55">
-      <c r="A86" s="45" t="inlineStr">
-        <is>
-          <t>T5.3.1</t>
-        </is>
-      </c>
-      <c r="B86" s="46" t="inlineStr">
-        <is>
-          <t>Conception de l'interface de monitoring</t>
-        </is>
-      </c>
-      <c r="C86" s="11" t="n"/>
-      <c r="D86" s="58" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="E86" s="11" t="n"/>
+      <c r="A86" s="42" t="inlineStr">
+        <is>
+          <t>T4.4</t>
+        </is>
+      </c>
+      <c r="B86" s="43" t="inlineStr">
+        <is>
+          <t>Actualisation dynamique Power BI</t>
+        </is>
+      </c>
+      <c r="C86" s="22" t="n"/>
+      <c r="D86" s="39" t="n"/>
+      <c r="E86" s="39" t="n"/>
       <c r="F86" s="11" t="n"/>
-      <c r="G86" s="58" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="H86" s="11" t="n"/>
-      <c r="I86" s="11" t="n"/>
-      <c r="J86" s="11" t="n"/>
-      <c r="K86" s="57" t="n"/>
+      <c r="G86" s="11" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="H86" s="11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I86" s="11" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="J86" s="11" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="K86" s="57" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="L86" s="11" t="n"/>
       <c r="M86" s="11" t="n"/>
       <c r="N86" s="11" t="n"/>
-      <c r="O86" s="11" t="n"/>
-      <c r="P86" s="49" t="n"/>
+      <c r="O86" s="11" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P86" s="13" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
     </row>
     <row r="87" ht="14.25" customHeight="1" s="55">
-      <c r="A87" s="47" t="inlineStr">
-        <is>
-          <t>T5.3.2</t>
-        </is>
-      </c>
-      <c r="B87" s="48" t="inlineStr">
-        <is>
-          <t>Developpement de la page Streamlit</t>
-        </is>
-      </c>
-      <c r="C87" s="11" t="n"/>
+      <c r="A87" s="44" t="inlineStr">
+        <is>
+          <t>T4.4.1</t>
+        </is>
+      </c>
+      <c r="B87" s="44" t="inlineStr">
+        <is>
+          <t>Connexion IA -&gt; Power BI : modification fichiers .pbix, datasets via API</t>
+        </is>
+      </c>
+      <c r="C87" s="58" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="D87" s="58" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="E87" s="11" t="n"/>
-      <c r="F87" s="11" t="n"/>
+      <c r="E87" s="58" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F87" s="58" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="G87" s="11" t="n"/>
-      <c r="H87" s="58" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="I87" s="11" t="n"/>
-      <c r="J87" s="11" t="n"/>
-      <c r="K87" s="57" t="n"/>
+      <c r="H87" s="11" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="I87" s="11" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="J87" s="58" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K87" s="57" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="L87" s="11" t="n"/>
       <c r="M87" s="11" t="n"/>
       <c r="N87" s="11" t="n"/>
-      <c r="O87" s="11" t="n"/>
-      <c r="P87" s="49" t="n"/>
+      <c r="O87" s="11" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P87" s="13" t="n"/>
     </row>
     <row r="88" ht="14.25" customHeight="1" s="55">
-      <c r="A88" s="50" t="inlineStr">
-        <is>
-          <t>T5.3.3</t>
-        </is>
-      </c>
-      <c r="B88" s="48" t="inlineStr">
-        <is>
-          <t>Lecture des logs du pipeline en temps reel</t>
-        </is>
-      </c>
-      <c r="C88" s="58" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="D88" s="11" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
+      <c r="A88" s="44" t="inlineStr">
+        <is>
+          <t>T4.4.2</t>
+        </is>
+      </c>
+      <c r="B88" s="44" t="inlineStr">
+        <is>
+          <t>Generation de visualisations par prompt : nouveaux graphiques et tableaux de bord</t>
+        </is>
+      </c>
+      <c r="C88" s="22" t="n"/>
+      <c r="D88" s="11" t="n"/>
       <c r="E88" s="11" t="n"/>
       <c r="F88" s="11" t="n"/>
-      <c r="G88" s="11" t="n"/>
-      <c r="H88" s="11" t="n"/>
-      <c r="I88" s="58" t="inlineStr">
+      <c r="G88" s="11" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="H88" s="11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I88" s="11" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
       <c r="J88" s="11" t="n"/>
-      <c r="K88" s="57" t="n"/>
+      <c r="K88" s="57" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L88" s="11" t="n"/>
       <c r="M88" s="11" t="n"/>
       <c r="N88" s="11" t="n"/>
-      <c r="O88" s="11" t="n"/>
-      <c r="P88" s="49" t="n"/>
+      <c r="O88" s="11" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P88" s="13" t="n"/>
     </row>
     <row r="89" ht="14.25" customHeight="1" s="55">
-      <c r="A89" s="52" t="inlineStr">
-        <is>
-          <t>T5.3.4</t>
-        </is>
-      </c>
-      <c r="B89" s="53" t="inlineStr">
-        <is>
-          <t>Affichage des alertes et indicateurs visuels</t>
+      <c r="A89" s="45" t="inlineStr">
+        <is>
+          <t>T4.4.3</t>
+        </is>
+      </c>
+      <c r="B89" s="46" t="inlineStr">
+        <is>
+          <t>Mise a jour des sources : mapping automatique des nouveaux champs vers Power BI</t>
         </is>
       </c>
       <c r="C89" s="11" t="n"/>
-      <c r="D89" s="58" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="E89" s="11" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="F89" s="11" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="G89" s="11" t="n"/>
-      <c r="H89" s="11" t="n"/>
-      <c r="I89" s="11" t="n"/>
-      <c r="J89" s="58" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="K89" s="57" t="n"/>
-      <c r="L89" s="11" t="n"/>
+      <c r="D89" s="11" t="n"/>
+      <c r="E89" s="11" t="n"/>
+      <c r="F89" s="58" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="G89" s="11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H89" s="11" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="I89" s="11" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="J89" s="11" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="K89" s="62" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L89" s="11" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="M89" s="11" t="n"/>
       <c r="N89" s="11" t="n"/>
       <c r="O89" s="11" t="n"/>
-      <c r="P89" s="49" t="n"/>
+      <c r="P89" s="13" t="n"/>
     </row>
     <row r="90" ht="14.25" customHeight="1" s="55">
-      <c r="A90" s="44" t="inlineStr">
-        <is>
-          <t>T5.4</t>
-        </is>
-      </c>
-      <c r="B90" s="44" t="inlineStr">
-        <is>
-          <t>Automatisation des flux (Pipeline)</t>
-        </is>
-      </c>
-      <c r="C90" s="22" t="n"/>
+      <c r="A90" s="47" t="inlineStr">
+        <is>
+          <t>T4.5</t>
+        </is>
+      </c>
+      <c r="B90" s="48" t="inlineStr">
+        <is>
+          <t>Controle client par prompts naturels</t>
+        </is>
+      </c>
+      <c r="C90" s="58" t="n"/>
       <c r="D90" s="11" t="n"/>
       <c r="E90" s="11" t="n"/>
-      <c r="F90" s="11" t="n"/>
-      <c r="G90" s="11" t="n"/>
-      <c r="H90" s="11" t="n"/>
-      <c r="I90" s="11" t="n"/>
+      <c r="F90" s="58" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="G90" s="11" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="H90" s="11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I90" s="11" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="J90" s="11" t="n"/>
-      <c r="K90" s="57" t="n"/>
+      <c r="K90" s="57" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="L90" s="11" t="n"/>
       <c r="M90" s="11" t="n"/>
-      <c r="N90" s="11" t="n"/>
+      <c r="N90" s="11" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="O90" s="11" t="n"/>
-      <c r="P90" s="49" t="n"/>
+      <c r="P90" s="13" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
     </row>
     <row r="91" ht="14.25" customHeight="1" s="55">
-      <c r="A91" s="45" t="inlineStr">
-        <is>
-          <t>T5.4.1</t>
-        </is>
-      </c>
-      <c r="B91" s="46" t="inlineStr">
-        <is>
-          <t>Ecriture du script Python principal du pipeline</t>
+      <c r="A91" s="47" t="inlineStr">
+        <is>
+          <t>T4.5.1</t>
+        </is>
+      </c>
+      <c r="B91" s="48" t="inlineStr">
+        <is>
+          <t>Interface de chat en langage naturel pour le client</t>
         </is>
       </c>
       <c r="C91" s="11" t="n"/>
-      <c r="D91" s="11" t="n"/>
-      <c r="E91" s="58" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="F91" s="49" t="n"/>
-      <c r="G91" s="49" t="n"/>
-      <c r="H91" s="49" t="n"/>
-      <c r="I91" s="49" t="n"/>
-      <c r="J91" s="49" t="n"/>
-      <c r="K91" s="62" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="L91" s="49" t="n"/>
-      <c r="M91" s="49" t="n"/>
-      <c r="N91" s="49" t="n"/>
-      <c r="O91" s="49" t="n"/>
-      <c r="P91" s="49" t="n"/>
+      <c r="D91" s="58" t="n"/>
+      <c r="E91" s="11" t="n"/>
+      <c r="F91" s="58" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="G91" s="11" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="H91" s="11" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="I91" s="11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J91" s="11" t="n"/>
+      <c r="K91" s="57" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L91" s="11" t="n"/>
+      <c r="M91" s="11" t="n"/>
+      <c r="N91" s="11" t="n"/>
+      <c r="O91" s="11" t="n"/>
+      <c r="P91" s="13" t="n"/>
     </row>
     <row r="92" ht="14.25" customHeight="1" s="55">
       <c r="A92" s="47" t="inlineStr">
         <is>
-          <t>T5.4.2</t>
+          <t>T4.5.2</t>
         </is>
       </c>
       <c r="B92" s="48" t="inlineStr">
         <is>
-          <t>Integration des etapes : reception → analyse → MAJ</t>
+          <t>Catalogue des actions disponibles avec exemples concrets de prompts</t>
         </is>
       </c>
       <c r="C92" s="58" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>R</t>
         </is>
       </c>
       <c r="D92" s="11" t="n"/>
-      <c r="E92" s="58" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="F92" s="49" t="n"/>
-      <c r="G92" s="49" t="n"/>
-      <c r="H92" s="49" t="n"/>
-      <c r="I92" s="49" t="n"/>
-      <c r="J92" s="49" t="n"/>
-      <c r="K92" s="64" t="n"/>
-      <c r="L92" s="49" t="n"/>
-      <c r="M92" s="49" t="n"/>
-      <c r="N92" s="49" t="n"/>
-      <c r="O92" s="49" t="n"/>
-      <c r="P92" s="49" t="n"/>
+      <c r="E92" s="58" t="n"/>
+      <c r="F92" s="11" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G92" s="11" t="n"/>
+      <c r="H92" s="11" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="I92" s="11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J92" s="11" t="n"/>
+      <c r="K92" s="57" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="L92" s="11" t="n"/>
+      <c r="M92" s="11" t="n"/>
+      <c r="N92" s="11" t="n"/>
+      <c r="O92" s="11" t="n"/>
+      <c r="P92" s="49" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
     </row>
     <row r="93" ht="14.25" customHeight="1" s="55">
-      <c r="A93" s="47" t="inlineStr">
-        <is>
-          <t>T5.4.3</t>
-        </is>
-      </c>
-      <c r="B93" s="48" t="inlineStr">
-        <is>
-          <t>Gestion des erreurs et fichiers de logs</t>
-        </is>
-      </c>
-      <c r="C93" s="11" t="n"/>
-      <c r="D93" s="65" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="E93" s="58" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="F93" s="49" t="n"/>
-      <c r="G93" s="49" t="n"/>
-      <c r="H93" s="49" t="n"/>
-      <c r="I93" s="49" t="n"/>
-      <c r="J93" s="49" t="n"/>
-      <c r="K93" s="64" t="n"/>
-      <c r="L93" s="49" t="n"/>
-      <c r="M93" s="49" t="n"/>
-      <c r="N93" s="49" t="n"/>
-      <c r="O93" s="49" t="n"/>
-      <c r="P93" s="49" t="n"/>
+      <c r="A93" s="50" t="inlineStr">
+        <is>
+          <t>T4.5.3</t>
+        </is>
+      </c>
+      <c r="B93" s="51" t="inlineStr">
+        <is>
+          <t>Gestion des erreurs et feedback : explication et alternatives si demande impossible</t>
+        </is>
+      </c>
+      <c r="C93" s="19" t="n"/>
+      <c r="D93" s="11" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="E93" s="11" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F93" s="58" t="n"/>
+      <c r="G93" s="11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H93" s="11" t="n"/>
+      <c r="I93" s="11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J93" s="11" t="n"/>
+      <c r="K93" s="57" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="L93" s="11" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="M93" s="11" t="n"/>
+      <c r="N93" s="11" t="n"/>
+      <c r="O93" s="11" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P93" s="11" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
     </row>
     <row r="94" ht="14.25" customHeight="1" s="55">
-      <c r="A94" s="50" t="inlineStr">
-        <is>
-          <t>T5.4.4</t>
-        </is>
-      </c>
-      <c r="B94" s="51" t="inlineStr">
-        <is>
-          <t>Automatisation et planification des executions</t>
-        </is>
-      </c>
-      <c r="C94" s="58" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="D94" s="11" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="E94" s="58" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="F94" s="11" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="G94" s="49" t="n"/>
-      <c r="H94" s="49" t="n"/>
-      <c r="I94" s="49" t="n"/>
-      <c r="J94" s="49" t="n"/>
-      <c r="K94" s="64" t="n"/>
-      <c r="L94" s="49" t="n"/>
-      <c r="M94" s="49" t="n"/>
-      <c r="N94" s="49" t="n"/>
-      <c r="O94" s="49" t="n"/>
+      <c r="A94" s="44" t="inlineStr">
+        <is>
+          <t>T4.6</t>
+        </is>
+      </c>
+      <c r="B94" s="44" t="inlineStr">
+        <is>
+          <t>Module de Nettoyage &amp; Normalisation</t>
+        </is>
+      </c>
+      <c r="C94" s="22" t="n"/>
+      <c r="D94" s="11" t="n"/>
+      <c r="E94" s="11" t="n"/>
+      <c r="F94" s="11" t="n"/>
+      <c r="G94" s="11" t="n"/>
+      <c r="H94" s="11" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="I94" s="11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J94" s="11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K94" s="57" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="L94" s="11" t="n"/>
+      <c r="M94" s="11" t="n"/>
+      <c r="N94" s="11" t="n"/>
+      <c r="O94" s="11" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="P94" s="49" t="n"/>
     </row>
     <row r="95" ht="14.25" customHeight="1" s="55">
-      <c r="A95" s="44" t="inlineStr">
-        <is>
-          <t>T5.5</t>
-        </is>
-      </c>
-      <c r="B95" s="44" t="inlineStr">
-        <is>
-          <t>Test final</t>
-        </is>
-      </c>
-      <c r="C95" s="22" t="n"/>
-      <c r="D95" s="11" t="n"/>
-      <c r="E95" s="49" t="n"/>
-      <c r="F95" s="49" t="n"/>
-      <c r="G95" s="49" t="n"/>
-      <c r="H95" s="49" t="n"/>
-      <c r="I95" s="49" t="n"/>
-      <c r="J95" s="49" t="n"/>
-      <c r="K95" s="64" t="n"/>
-      <c r="L95" s="49" t="n"/>
-      <c r="M95" s="49" t="n"/>
-      <c r="N95" s="49" t="n"/>
-      <c r="O95" s="49" t="n"/>
+      <c r="A95" s="45" t="inlineStr">
+        <is>
+          <t>T4.6.1</t>
+        </is>
+      </c>
+      <c r="B95" s="46" t="inlineStr">
+        <is>
+          <t>Scripts Regex : nettoyage chaines, extraction nombres, correction formats</t>
+        </is>
+      </c>
+      <c r="C95" s="11" t="n"/>
+      <c r="D95" s="58" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E95" s="11" t="n"/>
+      <c r="F95" s="11" t="n"/>
+      <c r="G95" s="58" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H95" s="11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I95" s="11" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="J95" s="11" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="K95" s="57" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L95" s="11" t="n"/>
+      <c r="M95" s="11" t="n"/>
+      <c r="N95" s="11" t="n"/>
+      <c r="O95" s="11" t="n"/>
       <c r="P95" s="49" t="n"/>
     </row>
     <row r="96" ht="14.25" customHeight="1" s="55">
-      <c r="A96" s="45" t="inlineStr">
-        <is>
-          <t>T5.5.1</t>
-        </is>
-      </c>
-      <c r="B96" s="46" t="inlineStr">
-        <is>
-          <t>Simulation donnees : test pipeline bout en bout</t>
+      <c r="A96" s="47" t="inlineStr">
+        <is>
+          <t>T4.6.2</t>
+        </is>
+      </c>
+      <c r="B96" s="48" t="inlineStr">
+        <is>
+          <t>Standardisation : conversion devises, uniformisation dates ISO 8601</t>
         </is>
       </c>
       <c r="C96" s="11" t="n"/>
@@ -4870,153 +5226,198 @@
           <t>R</t>
         </is>
       </c>
-      <c r="E96" s="58" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="F96" s="62" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="G96" s="49" t="n"/>
-      <c r="H96" s="49" t="n"/>
-      <c r="I96" s="49" t="n"/>
-      <c r="J96" s="49" t="n"/>
-      <c r="K96" s="64" t="n"/>
-      <c r="L96" s="49" t="n"/>
-      <c r="M96" s="49" t="n"/>
-      <c r="N96" s="49" t="n"/>
-      <c r="O96" s="49" t="n"/>
+      <c r="E96" s="11" t="n"/>
+      <c r="F96" s="11" t="n"/>
+      <c r="G96" s="11" t="n"/>
+      <c r="H96" s="58" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="I96" s="11" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="J96" s="11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K96" s="57" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="L96" s="11" t="n"/>
+      <c r="M96" s="11" t="n"/>
+      <c r="N96" s="11" t="n"/>
+      <c r="O96" s="11" t="n"/>
       <c r="P96" s="49" t="n"/>
     </row>
     <row r="97" ht="14.25" customHeight="1" s="55">
-      <c r="A97" s="47" t="inlineStr">
-        <is>
-          <t>T5.5.2</t>
+      <c r="A97" s="50" t="inlineStr">
+        <is>
+          <t>T4.6.3</t>
         </is>
       </c>
       <c r="B97" s="48" t="inlineStr">
         <is>
-          <t>Verification affichage Dashboard apres pipeline</t>
-        </is>
-      </c>
-      <c r="C97" s="11" t="n"/>
-      <c r="D97" s="11" t="n"/>
-      <c r="F97" s="58" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="G97" s="58" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="H97" s="49" t="n"/>
-      <c r="I97" s="49" t="n"/>
-      <c r="J97" s="49" t="n"/>
-      <c r="K97" s="64" t="n"/>
-      <c r="L97" s="49" t="n"/>
-      <c r="M97" s="49" t="n"/>
-      <c r="N97" s="49" t="n"/>
-      <c r="O97" s="49" t="n"/>
-      <c r="P97" s="49" t="n"/>
+          <t>Deduplonnage et integrite : SIREN 9 chiffres, email valide, pas de doublons</t>
+        </is>
+      </c>
+      <c r="C97" s="58" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D97" s="11" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="E97" s="11" t="n"/>
+      <c r="F97" s="11" t="n"/>
+      <c r="G97" s="11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H97" s="11" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="I97" s="58" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="J97" s="11" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="K97" s="57" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L97" s="11" t="n"/>
+      <c r="M97" s="11" t="n"/>
+      <c r="N97" s="11" t="n"/>
+      <c r="O97" s="11" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P97" s="49" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
     </row>
     <row r="98" ht="14.25" customHeight="1" s="55">
-      <c r="A98" s="47" t="inlineStr">
-        <is>
-          <t>T5.5.3</t>
-        </is>
-      </c>
-      <c r="B98" s="48" t="inlineStr">
-        <is>
-          <t>Verification interface monitoring pendant tests</t>
+      <c r="A98" s="52" t="inlineStr">
+        <is>
+          <t>T5</t>
+        </is>
+      </c>
+      <c r="B98" s="53" t="inlineStr">
+        <is>
+          <t>Finalisation</t>
         </is>
       </c>
       <c r="C98" s="11" t="n"/>
-      <c r="D98" s="11" t="n"/>
-      <c r="E98" s="11" t="n"/>
-      <c r="F98" s="49" t="n"/>
-      <c r="G98" s="49" t="n"/>
-      <c r="H98" s="66" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="I98" s="58" t="inlineStr">
+      <c r="D98" s="58" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E98" s="11" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F98" s="11" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G98" s="11" t="n"/>
+      <c r="H98" s="11" t="n"/>
+      <c r="I98" s="11" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
       <c r="J98" s="58" t="inlineStr">
         <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="K98" s="57" t="n"/>
-      <c r="L98" s="49" t="n"/>
-      <c r="M98" s="49" t="n"/>
-      <c r="N98" s="49" t="n"/>
-      <c r="O98" s="49" t="n"/>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K98" s="57" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L98" s="11" t="n"/>
+      <c r="M98" s="11" t="n"/>
+      <c r="N98" s="11" t="n"/>
+      <c r="O98" s="11" t="n"/>
       <c r="P98" s="49" t="n"/>
     </row>
     <row r="99" ht="14.25" customHeight="1" s="55">
-      <c r="A99" s="50" t="inlineStr">
-        <is>
-          <t>T5.5.4</t>
-        </is>
-      </c>
-      <c r="B99" s="51" t="inlineStr">
-        <is>
-          <t>Redaction du rapport de tests finaux</t>
-        </is>
-      </c>
-      <c r="C99" s="11" t="n"/>
+      <c r="A99" s="44" t="inlineStr">
+        <is>
+          <t>T5.1</t>
+        </is>
+      </c>
+      <c r="B99" s="44" t="inlineStr">
+        <is>
+          <t>[FORMATION] Data : Power BI &amp; Streamlit</t>
+        </is>
+      </c>
+      <c r="C99" s="22" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="D99" s="11" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>R</t>
         </is>
       </c>
       <c r="E99" s="11" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>R</t>
         </is>
       </c>
       <c r="F99" s="11" t="inlineStr">
         <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="G99" s="11" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="H99" s="58" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="I99" s="58" t="inlineStr">
+          <t>R</t>
+        </is>
+      </c>
+      <c r="G99" s="11" t="n"/>
+      <c r="H99" s="11" t="n"/>
+      <c r="I99" s="11" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
       <c r="J99" s="11" t="inlineStr">
         <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="K99" s="57" t="n"/>
-      <c r="L99" s="11" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="M99" s="49" t="n"/>
-      <c r="N99" s="49" t="n"/>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K99" s="57" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="L99" s="11" t="n"/>
+      <c r="M99" s="11" t="n"/>
+      <c r="N99" s="11" t="n"/>
       <c r="O99" s="11" t="inlineStr">
         <is>
           <t>C</t>
@@ -5025,25 +5426,41 @@
       <c r="P99" s="49" t="n"/>
     </row>
     <row r="100" ht="14.25" customHeight="1" s="55">
-      <c r="A100" s="44" t="inlineStr">
-        <is>
-          <t>T5.6</t>
-        </is>
-      </c>
-      <c r="B100" s="44" t="inlineStr">
-        <is>
-          <t>Clôture &amp; Transfert</t>
-        </is>
-      </c>
-      <c r="C100" s="22" t="n"/>
+      <c r="A100" s="45" t="inlineStr">
+        <is>
+          <t>T5.2</t>
+        </is>
+      </c>
+      <c r="B100" s="46" t="inlineStr">
+        <is>
+          <t>Conception du Dashboard Power BI</t>
+        </is>
+      </c>
+      <c r="C100" s="11" t="n"/>
       <c r="D100" s="11" t="n"/>
-      <c r="E100" s="11" t="n"/>
+      <c r="E100" s="58" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="F100" s="49" t="n"/>
       <c r="G100" s="49" t="n"/>
       <c r="H100" s="49" t="n"/>
-      <c r="I100" s="49" t="n"/>
-      <c r="J100" s="49" t="n"/>
-      <c r="K100" s="64" t="n"/>
+      <c r="I100" s="49" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="J100" s="49" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="K100" s="62" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="L100" s="49" t="n"/>
       <c r="M100" s="49" t="n"/>
       <c r="N100" s="49" t="n"/>
@@ -5051,87 +5468,95 @@
       <c r="P100" s="49" t="n"/>
     </row>
     <row r="101" ht="14.25" customHeight="1" s="55">
-      <c r="A101" s="45" t="inlineStr">
-        <is>
-          <t>T5.6.1</t>
-        </is>
-      </c>
-      <c r="B101" s="46" t="inlineStr">
-        <is>
-          <t>Depot des livrables sur le Drive projet</t>
+      <c r="A101" s="47" t="inlineStr">
+        <is>
+          <t>T5.2.1</t>
+        </is>
+      </c>
+      <c r="B101" s="48" t="inlineStr">
+        <is>
+          <t>Conception de la structure du Dashboard</t>
         </is>
       </c>
       <c r="C101" s="58" t="inlineStr">
         <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="D101" s="11" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="E101" s="11" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="F101" s="11" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="G101" s="11" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="H101" s="11" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="I101" s="11" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="J101" s="58" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="K101" s="57" t="n"/>
-      <c r="L101" s="11" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D101" s="11" t="n"/>
+      <c r="E101" s="58" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F101" s="49" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="G101" s="49" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="H101" s="49" t="n"/>
+      <c r="I101" s="49" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="J101" s="49" t="n"/>
+      <c r="K101" s="64" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L101" s="49" t="n"/>
       <c r="M101" s="49" t="n"/>
-      <c r="N101" s="49" t="n"/>
+      <c r="N101" s="49" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="O101" s="49" t="n"/>
-      <c r="P101" s="11" t="inlineStr">
-        <is>
-          <t>I</t>
+      <c r="P101" s="49" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
     </row>
     <row r="102" ht="14.25" customHeight="1" s="55">
       <c r="A102" s="47" t="inlineStr">
         <is>
-          <t>T5.6.2</t>
+          <t>T5.2.2</t>
         </is>
       </c>
       <c r="B102" s="48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Redaction du guide utilisateur </t>
-        </is>
-      </c>
-      <c r="C102" s="11" t="n"/>
-      <c r="D102" s="11" t="n"/>
-      <c r="E102" s="11" t="n"/>
-      <c r="F102" s="49" t="n"/>
-      <c r="G102" s="58" t="inlineStr">
+          <t>Developpement des rapports et visualisations Power BI</t>
+        </is>
+      </c>
+      <c r="C102" s="11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D102" s="65" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E102" s="58" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F102" s="49" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="G102" s="49" t="inlineStr">
         <is>
           <t>R</t>
         </is>
@@ -5139,46 +5564,786 @@
       <c r="H102" s="49" t="n"/>
       <c r="I102" s="49" t="n"/>
       <c r="J102" s="49" t="n"/>
-      <c r="K102" s="62" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="L102" s="11" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
+      <c r="K102" s="64" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L102" s="49" t="n"/>
       <c r="M102" s="49" t="n"/>
       <c r="N102" s="49" t="n"/>
       <c r="O102" s="49" t="n"/>
-      <c r="P102" s="11" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-    </row>
-    <row r="103" ht="14.25" customHeight="1" s="55"/>
-    <row r="104" ht="14.25" customHeight="1" s="55"/>
-    <row r="105" ht="14.25" customHeight="1" s="55"/>
-    <row r="106" ht="14.25" customHeight="1" s="55"/>
-    <row r="107" ht="14.25" customHeight="1" s="55"/>
-    <row r="108" ht="14.25" customHeight="1" s="55"/>
-    <row r="109" ht="14.25" customHeight="1" s="55"/>
-    <row r="110" ht="14.25" customHeight="1" s="55"/>
-    <row r="111" ht="14.25" customHeight="1" s="55"/>
-    <row r="112" ht="14.25" customHeight="1" s="55"/>
-    <row r="113" ht="14.25" customHeight="1" s="55"/>
-    <row r="114" ht="14.25" customHeight="1" s="55"/>
-    <row r="115" ht="14.25" customHeight="1" s="55"/>
-    <row r="116" ht="14.25" customHeight="1" s="55"/>
-    <row r="117" ht="14.25" customHeight="1" s="55"/>
-    <row r="118" ht="14.25" customHeight="1" s="55"/>
-    <row r="119" ht="14.25" customHeight="1" s="55"/>
-    <row r="120" ht="14.25" customHeight="1" s="55"/>
-    <row r="121" ht="14.25" customHeight="1" s="55"/>
-    <row r="122" ht="14.25" customHeight="1" s="55"/>
-    <row r="123" ht="14.25" customHeight="1" s="55"/>
+      <c r="P102" s="49" t="n"/>
+    </row>
+    <row r="103" ht="14.25" customHeight="1" s="55">
+      <c r="A103" s="50" t="inlineStr">
+        <is>
+          <t>T5.2.3</t>
+        </is>
+      </c>
+      <c r="B103" s="51" t="inlineStr">
+        <is>
+          <t>Connexion donnees -&gt; Power BI (Power Query)</t>
+        </is>
+      </c>
+      <c r="C103" s="58" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D103" s="11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E103" s="58" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F103" s="11" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="G103" s="49" t="n"/>
+      <c r="H103" s="49" t="n"/>
+      <c r="I103" s="49" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J103" s="49" t="n"/>
+      <c r="K103" s="64" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="L103" s="49" t="n"/>
+      <c r="M103" s="49" t="n"/>
+      <c r="N103" s="49" t="n"/>
+      <c r="O103" s="49" t="n"/>
+      <c r="P103" s="49" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="14.25" customHeight="1" s="55">
+      <c r="A104" s="44" t="inlineStr">
+        <is>
+          <t>T5.2.4</t>
+        </is>
+      </c>
+      <c r="B104" s="44" t="inlineStr">
+        <is>
+          <t>Ecriture des formules DAX et indicateurs calcules</t>
+        </is>
+      </c>
+      <c r="C104" s="22" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D104" s="11" t="n"/>
+      <c r="E104" s="49" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F104" s="49" t="n"/>
+      <c r="G104" s="49" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H104" s="49" t="n"/>
+      <c r="I104" s="49" t="n"/>
+      <c r="J104" s="49" t="n"/>
+      <c r="K104" s="64" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="L104" s="49" t="n"/>
+      <c r="M104" s="49" t="n"/>
+      <c r="N104" s="49" t="n"/>
+      <c r="O104" s="49" t="n"/>
+      <c r="P104" s="49" t="n"/>
+    </row>
+    <row r="105" ht="14.25" customHeight="1" s="55">
+      <c r="A105" s="45" t="inlineStr">
+        <is>
+          <t>T5.2.5</t>
+        </is>
+      </c>
+      <c r="B105" s="46" t="inlineStr">
+        <is>
+          <t>Validation et livraison du Dashboard</t>
+        </is>
+      </c>
+      <c r="C105" s="11" t="n"/>
+      <c r="D105" s="58" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="E105" s="58" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F105" s="62" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G105" s="49" t="n"/>
+      <c r="H105" s="49" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="I105" s="49" t="n"/>
+      <c r="J105" s="49" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K105" s="64" t="n"/>
+      <c r="L105" s="49" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="M105" s="49" t="n"/>
+      <c r="N105" s="49" t="n"/>
+      <c r="O105" s="49" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P105" s="49" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="14.25" customHeight="1" s="55">
+      <c r="A106" s="47" t="inlineStr">
+        <is>
+          <t>T5.3</t>
+        </is>
+      </c>
+      <c r="B106" s="48" t="inlineStr">
+        <is>
+          <t>Interface de Pilotage (Monitoring)</t>
+        </is>
+      </c>
+      <c r="C106" s="11" t="n"/>
+      <c r="D106" s="11" t="n"/>
+      <c r="F106" s="58" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="G106" s="58" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H106" s="49" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I106" s="49" t="n"/>
+      <c r="J106" s="49" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="K106" s="64" t="n"/>
+      <c r="L106" s="49" t="n"/>
+      <c r="M106" s="49" t="n"/>
+      <c r="N106" s="49" t="n"/>
+      <c r="O106" s="49" t="n"/>
+      <c r="P106" s="49" t="n"/>
+    </row>
+    <row r="107" ht="14.25" customHeight="1" s="55">
+      <c r="A107" s="47" t="inlineStr">
+        <is>
+          <t>T5.3.1</t>
+        </is>
+      </c>
+      <c r="B107" s="48" t="inlineStr">
+        <is>
+          <t>Conception de l'interface de monitoring</t>
+        </is>
+      </c>
+      <c r="C107" s="11" t="n"/>
+      <c r="D107" s="11" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E107" s="11" t="n"/>
+      <c r="F107" s="49" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G107" s="49" t="n"/>
+      <c r="H107" s="66" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="I107" s="58" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="J107" s="58" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K107" s="57" t="n"/>
+      <c r="L107" s="49" t="n"/>
+      <c r="M107" s="49" t="n"/>
+      <c r="N107" s="49" t="n"/>
+      <c r="O107" s="49" t="n"/>
+      <c r="P107" s="49" t="n"/>
+    </row>
+    <row r="108" ht="14.25" customHeight="1" s="55">
+      <c r="A108" s="50" t="inlineStr">
+        <is>
+          <t>T5.3.2</t>
+        </is>
+      </c>
+      <c r="B108" s="51" t="inlineStr">
+        <is>
+          <t>Developpement de la page Streamlit</t>
+        </is>
+      </c>
+      <c r="C108" s="11" t="n"/>
+      <c r="D108" s="11" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E108" s="11" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F108" s="11" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G108" s="11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H108" s="58" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I108" s="58" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J108" s="11" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="K108" s="57" t="n"/>
+      <c r="L108" s="11" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="M108" s="49" t="n"/>
+      <c r="N108" s="49" t="n"/>
+      <c r="O108" s="11" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P108" s="49" t="n"/>
+    </row>
+    <row r="109" ht="14.25" customHeight="1" s="55">
+      <c r="A109" s="44" t="inlineStr">
+        <is>
+          <t>T5.3.3</t>
+        </is>
+      </c>
+      <c r="B109" s="44" t="inlineStr">
+        <is>
+          <t>Lecture des logs du pipeline en temps reel</t>
+        </is>
+      </c>
+      <c r="C109" s="22" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D109" s="11" t="n"/>
+      <c r="E109" s="11" t="n"/>
+      <c r="F109" s="49" t="n"/>
+      <c r="G109" s="49" t="n"/>
+      <c r="H109" s="49" t="n"/>
+      <c r="I109" s="49" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J109" s="49" t="n"/>
+      <c r="K109" s="64" t="n"/>
+      <c r="L109" s="49" t="n"/>
+      <c r="M109" s="49" t="n"/>
+      <c r="N109" s="49" t="n"/>
+      <c r="O109" s="49" t="n"/>
+      <c r="P109" s="49" t="n"/>
+    </row>
+    <row r="110" ht="14.25" customHeight="1" s="55">
+      <c r="A110" s="45" t="inlineStr">
+        <is>
+          <t>T5.3.4</t>
+        </is>
+      </c>
+      <c r="B110" s="46" t="inlineStr">
+        <is>
+          <t>Affichage des alertes et indicateurs visuels</t>
+        </is>
+      </c>
+      <c r="C110" s="58" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D110" s="11" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E110" s="11" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F110" s="11" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G110" s="11" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="H110" s="11" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="I110" s="11" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="J110" s="58" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K110" s="57" t="n"/>
+      <c r="L110" s="11" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="M110" s="49" t="n"/>
+      <c r="N110" s="49" t="n"/>
+      <c r="O110" s="49" t="n"/>
+      <c r="P110" s="11" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="14.25" customHeight="1" s="55">
+      <c r="A111" s="47" t="inlineStr">
+        <is>
+          <t>T5.4</t>
+        </is>
+      </c>
+      <c r="B111" s="48" t="inlineStr">
+        <is>
+          <t>Automatisation des flux (Pipeline)</t>
+        </is>
+      </c>
+      <c r="C111" s="11" t="n"/>
+      <c r="D111" s="11" t="n"/>
+      <c r="E111" s="11" t="n"/>
+      <c r="F111" s="49" t="n"/>
+      <c r="G111" s="58" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="H111" s="49" t="n"/>
+      <c r="I111" s="49" t="n"/>
+      <c r="J111" s="49" t="n"/>
+      <c r="K111" s="62" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L111" s="11" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="M111" s="49" t="n"/>
+      <c r="N111" s="49" t="n"/>
+      <c r="O111" s="49" t="n"/>
+      <c r="P111" s="11" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="14.25" customHeight="1" s="55">
+      <c r="A112" s="0" t="inlineStr">
+        <is>
+          <t>T5.4.1</t>
+        </is>
+      </c>
+      <c r="B112" s="0" t="inlineStr">
+        <is>
+          <t>Ecriture du script Python principal du pipeline</t>
+        </is>
+      </c>
+      <c r="E112" s="0" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="K112" s="0" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="14.25" customHeight="1" s="55">
+      <c r="A113" s="0" t="inlineStr">
+        <is>
+          <t>T5.4.2</t>
+        </is>
+      </c>
+      <c r="B113" s="0" t="inlineStr">
+        <is>
+          <t>Integration des etapes : reception -&gt; analyse -&gt; MAJ</t>
+        </is>
+      </c>
+      <c r="C113" s="0" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E113" s="0" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="14.25" customHeight="1" s="55">
+      <c r="A114" s="0" t="inlineStr">
+        <is>
+          <t>T5.4.3</t>
+        </is>
+      </c>
+      <c r="B114" s="0" t="inlineStr">
+        <is>
+          <t>Gestion des erreurs et fichiers de logs</t>
+        </is>
+      </c>
+      <c r="D114" s="0" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E114" s="0" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="14.25" customHeight="1" s="55">
+      <c r="A115" s="0" t="inlineStr">
+        <is>
+          <t>T5.4.4</t>
+        </is>
+      </c>
+      <c r="B115" s="0" t="inlineStr">
+        <is>
+          <t>Automatisation et planification des executions</t>
+        </is>
+      </c>
+      <c r="C115" s="0" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E115" s="0" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="14.25" customHeight="1" s="55">
+      <c r="A116" s="0" t="inlineStr">
+        <is>
+          <t>T5.5</t>
+        </is>
+      </c>
+      <c r="B116" s="0" t="inlineStr">
+        <is>
+          <t>Test final</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="14.25" customHeight="1" s="55">
+      <c r="A117" s="0" t="inlineStr">
+        <is>
+          <t>T5.5.1</t>
+        </is>
+      </c>
+      <c r="B117" s="0" t="inlineStr">
+        <is>
+          <t>Simulation donnees : test pipeline bout en bout</t>
+        </is>
+      </c>
+      <c r="D117" s="0" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E117" s="0" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F117" s="0" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L117" s="0" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="14.25" customHeight="1" s="55">
+      <c r="A118" s="0" t="inlineStr">
+        <is>
+          <t>T5.5.2</t>
+        </is>
+      </c>
+      <c r="B118" s="0" t="inlineStr">
+        <is>
+          <t>Verification affichage Dashboard apres pipeline</t>
+        </is>
+      </c>
+      <c r="F118" s="0" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="H118" s="0" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="14.25" customHeight="1" s="55">
+      <c r="A119" s="0" t="inlineStr">
+        <is>
+          <t>T5.5.3</t>
+        </is>
+      </c>
+      <c r="B119" s="0" t="inlineStr">
+        <is>
+          <t>Verification interface monitoring pendant tests</t>
+        </is>
+      </c>
+      <c r="H119" s="0" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I119" s="0" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="J119" s="0" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="14.25" customHeight="1" s="55">
+      <c r="A120" s="0" t="inlineStr">
+        <is>
+          <t>T5.5.4</t>
+        </is>
+      </c>
+      <c r="B120" s="0" t="inlineStr">
+        <is>
+          <t>Redaction du rapport de tests finaux</t>
+        </is>
+      </c>
+      <c r="H120" s="0" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="I120" s="0" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J120" s="0" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="L120" s="0" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="O120" s="0" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="14.25" customHeight="1" s="55">
+      <c r="A121" s="0" t="inlineStr">
+        <is>
+          <t>T5.6</t>
+        </is>
+      </c>
+      <c r="B121" s="0" t="inlineStr">
+        <is>
+          <t>Cloture &amp; Transfert</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="14.25" customHeight="1" s="55">
+      <c r="A122" s="0" t="inlineStr">
+        <is>
+          <t>T5.6.1</t>
+        </is>
+      </c>
+      <c r="B122" s="0" t="inlineStr">
+        <is>
+          <t>Depot des livrables sur le Drive projet</t>
+        </is>
+      </c>
+      <c r="C122" s="0" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D122" s="0" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="E122" s="0" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F122" s="0" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G122" s="0" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="H122" s="0" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="I122" s="0" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="J122" s="0" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L122" s="0" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="P122" s="0" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="14.25" customHeight="1" s="55">
+      <c r="A123" s="0" t="inlineStr">
+        <is>
+          <t>T5.6.2</t>
+        </is>
+      </c>
+      <c r="B123" s="0" t="inlineStr">
+        <is>
+          <t>Redaction du guide utilisateur</t>
+        </is>
+      </c>
+      <c r="G123" s="0" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="K123" s="0" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L123" s="0" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="P123" s="0" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+    </row>
     <row r="124" ht="14.25" customHeight="1" s="55"/>
     <row r="125" ht="14.25" customHeight="1" s="55"/>
     <row r="126" ht="14.25" customHeight="1" s="55"/>
